--- a/data/raw/Democracy in Action/review/dia_2012_newspapers_review.xlsx
+++ b/data/raw/Democracy in Action/review/dia_2012_newspapers_review.xlsx
@@ -9,17 +9,23 @@
     <sheet name="review" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review'!$A$1:$Q$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review'!$A$1:$S$59</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="287">
   <si>
     <t xml:space="preserve">row_id</t>
   </si>
   <si>
+    <t xml:space="preserve">review_action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review_note</t>
+  </si>
+  <si>
     <t xml:space="preserve">contest_id</t>
   </si>
   <si>
@@ -69,6 +75,9 @@
   </si>
   <si>
     <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">2012R</t>
@@ -1212,22 +1221,24 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="15.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="40.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="22.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="21.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="10.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="16.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="40.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="18.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="18.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="40.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="11.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="80.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="40.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="8.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="8.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="40.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="22.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="21.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="8.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="10.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="16.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="40.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="18.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="40.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="11.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="80.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1282,2371 +1293,2725 @@
       <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
-      <c r="P2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>23</v>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="1" t="s">
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="N3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
       <c r="Q3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>37</v>
+      <c r="S4" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="N5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>42</v>
+      <c r="S5" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>47</v>
+      <c r="S6" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>52</v>
+      <c r="S7" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>57</v>
+      <c r="S8" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+        <v>62</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="M9" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="N9" s="1"/>
-      <c r="O9" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
       <c r="Q9" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J10" s="1"/>
-      <c r="K10" s="1" t="s">
-        <v>67</v>
-      </c>
+      <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
+      <c r="M10" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="N10" s="1"/>
-      <c r="O10" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="I11" s="1" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="M11" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>73</v>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J12" s="1"/>
-      <c r="K12" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J13" s="1"/>
-      <c r="K13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
       <c r="Q13" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J14" s="1"/>
-      <c r="K14" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="K14" s="1"/>
       <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
+      <c r="M14" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="N14" s="1"/>
-      <c r="O14" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
       <c r="Q14" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J15" s="1"/>
-      <c r="K15" s="1" t="s">
-        <v>91</v>
-      </c>
+      <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="N15" s="1"/>
-      <c r="O15" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
       <c r="Q15" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J16" s="1"/>
-      <c r="K16" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="K16" s="1"/>
       <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
+      <c r="M16" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="N16" s="1"/>
-      <c r="O16" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
       <c r="Q16" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J17" s="1"/>
-      <c r="K17" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
+      <c r="M17" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="N17" s="1"/>
-      <c r="O17" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
       <c r="Q17" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="I18" s="1" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
       <c r="Q18" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="R19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>110</v>
+      <c r="S19" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="R20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>115</v>
+      <c r="S20" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="I21" s="1" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
+      <c r="M21" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="N21" s="1"/>
-      <c r="O21" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
       <c r="Q21" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J22" s="1"/>
-      <c r="K22" s="1" t="s">
-        <v>91</v>
-      </c>
+      <c r="K22" s="1"/>
       <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
+      <c r="M22" s="1" t="s">
+        <v>94</v>
+      </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
-      <c r="P22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>122</v>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J23" s="1"/>
-      <c r="K23" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="K23" s="1"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
+      <c r="M23" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
-      <c r="P23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>125</v>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>129</v>
+      <c r="S24" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J25" s="1"/>
-      <c r="K25" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
       <c r="Q25" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="R26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>140</v>
+      <c r="S26" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>145</v>
+      <c r="S27" s="1" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="N28" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="R28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>149</v>
+      <c r="S28" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J29" s="1"/>
-      <c r="K29" s="1" t="s">
-        <v>152</v>
-      </c>
+      <c r="K29" s="1"/>
       <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
+      <c r="M29" s="1" t="s">
+        <v>155</v>
+      </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
-      <c r="P29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>153</v>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J30" s="1"/>
-      <c r="K30" s="1" t="s">
-        <v>132</v>
-      </c>
+      <c r="K30" s="1"/>
       <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
+      <c r="M30" s="1" t="s">
+        <v>135</v>
+      </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
-      <c r="P30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>156</v>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>158</v>
+        <v>23</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H31" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="I31" s="1" t="s">
-        <v>159</v>
+        <v>24</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
+      <c r="M31" s="1" t="s">
+        <v>135</v>
+      </c>
       <c r="N31" s="1"/>
-      <c r="O31" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
+        <v>62</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J32" s="1"/>
-      <c r="K32" s="1" t="s">
-        <v>164</v>
-      </c>
+      <c r="K32" s="1"/>
       <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
+      <c r="M32" s="1" t="s">
+        <v>167</v>
+      </c>
       <c r="N32" s="1"/>
-      <c r="O32" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="R33" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>171</v>
+      <c r="S33" s="1" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="R34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>176</v>
+      <c r="S34" s="1" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="R35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>180</v>
+      <c r="S35" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>182</v>
+        <v>23</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J36" s="1"/>
-      <c r="K36" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
       <c r="Q36" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="R37" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>190</v>
+      <c r="S37" s="1" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="R38" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="P38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q38" s="1" t="s">
-        <v>194</v>
+      <c r="S38" s="1" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>196</v>
+        <v>23</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J39" s="1"/>
-      <c r="K39" s="1" t="s">
-        <v>188</v>
-      </c>
+      <c r="K39" s="1"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
+      <c r="M39" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
-      <c r="P39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q39" s="1" t="s">
-        <v>197</v>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S39" s="1" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="R40" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q40" s="1" t="s">
-        <v>202</v>
+      <c r="S40" s="1" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="R41" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q41" s="1" t="s">
-        <v>207</v>
+      <c r="S41" s="1" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="R42" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q42" s="1" t="s">
-        <v>212</v>
+      <c r="S42" s="1" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="R43" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="P43" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q43" s="1" t="s">
-        <v>217</v>
+      <c r="S43" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E44" s="1" t="s">
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="R44" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q44" s="1" t="s">
-        <v>221</v>
+      <c r="S44" s="1" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="R45" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="P45" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q45" s="1" t="s">
-        <v>226</v>
+      <c r="S45" s="1" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>228</v>
+        <v>23</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J46" s="1"/>
-      <c r="K46" s="1" t="s">
-        <v>200</v>
-      </c>
+      <c r="K46" s="1"/>
       <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
+      <c r="M46" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="N46" s="1"/>
-      <c r="O46" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="P46" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
       <c r="Q46" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
+      </c>
+      <c r="R46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>232</v>
+        <v>23</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J47" s="1"/>
-      <c r="K47" s="1" t="s">
-        <v>233</v>
-      </c>
+      <c r="K47" s="1"/>
       <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
+      <c r="M47" s="1" t="s">
+        <v>236</v>
+      </c>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
-      <c r="P47" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q47" s="1" t="s">
-        <v>234</v>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S47" s="1" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>236</v>
+        <v>23</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J48" s="1"/>
-      <c r="K48" s="1" t="s">
-        <v>237</v>
-      </c>
+      <c r="K48" s="1"/>
       <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
+      <c r="M48" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
-      <c r="P48" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q48" s="1" t="s">
-        <v>238</v>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S48" s="1" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>240</v>
+        <v>23</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J49" s="1"/>
-      <c r="K49" s="1" t="s">
-        <v>241</v>
-      </c>
+      <c r="K49" s="1"/>
       <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
+      <c r="M49" s="1" t="s">
+        <v>244</v>
+      </c>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
-      <c r="P49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>242</v>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S49" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>244</v>
+        <v>23</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J50" s="1"/>
-      <c r="K50" s="1" t="s">
-        <v>233</v>
-      </c>
+      <c r="K50" s="1"/>
       <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
+      <c r="M50" s="1" t="s">
+        <v>236</v>
+      </c>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
-      <c r="P50" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q50" s="1" t="s">
-        <v>245</v>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S50" s="1" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>247</v>
+        <v>23</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J51" s="1"/>
-      <c r="K51" s="1" t="s">
-        <v>233</v>
-      </c>
+      <c r="K51" s="1"/>
       <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
+      <c r="M51" s="1" t="s">
+        <v>236</v>
+      </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
-      <c r="P51" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>248</v>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S51" s="1" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>250</v>
+        <v>23</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J52" s="1"/>
-      <c r="K52" s="1" t="s">
-        <v>251</v>
-      </c>
+      <c r="K52" s="1"/>
       <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
+      <c r="M52" s="1" t="s">
+        <v>254</v>
+      </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
-      <c r="P52" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q52" s="1" t="s">
-        <v>252</v>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S52" s="1" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>254</v>
+        <v>23</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J53" s="1"/>
-      <c r="K53" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="K53" s="1"/>
       <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
+      <c r="M53" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
-      <c r="P53" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>255</v>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S53" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="O54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>260</v>
+      <c r="S54" s="1" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>262</v>
+        <v>23</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J55" s="1"/>
-      <c r="K55" s="1" t="s">
-        <v>263</v>
-      </c>
+      <c r="K55" s="1"/>
       <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
+      <c r="M55" s="1" t="s">
+        <v>266</v>
+      </c>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
-      <c r="P55" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>264</v>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S55" s="1" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>266</v>
+        <v>23</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J56" s="1"/>
-      <c r="K56" s="1" t="s">
-        <v>267</v>
-      </c>
+      <c r="K56" s="1"/>
       <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
+      <c r="M56" s="1" t="s">
+        <v>270</v>
+      </c>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
-      <c r="P56" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>268</v>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S56" s="1" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>273</v>
+      <c r="S57" s="1" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q58" s="1" t="s">
-        <v>277</v>
+      <c r="S58" s="1" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E59" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
+      <c r="Q59" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="R59" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="P59" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q59" s="1" t="s">
-        <v>283</v>
+      <c r="S59" s="1" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="60">
@@ -3667,6 +4032,8 @@
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
       <c r="Q60" s="1"/>
+      <c r="R60" s="1"/>
+      <c r="S60" s="1"/>
     </row>
     <row r="61">
       <c r="A61" s="1"/>
@@ -3686,6 +4053,8 @@
       <c r="O61" s="1"/>
       <c r="P61" s="1"/>
       <c r="Q61" s="1"/>
+      <c r="R61" s="1"/>
+      <c r="S61" s="1"/>
     </row>
     <row r="62">
       <c r="A62" s="1"/>
@@ -3705,6 +4074,8 @@
       <c r="O62" s="1"/>
       <c r="P62" s="1"/>
       <c r="Q62" s="1"/>
+      <c r="R62" s="1"/>
+      <c r="S62" s="1"/>
     </row>
     <row r="63">
       <c r="A63" s="1"/>
@@ -3724,6 +4095,8 @@
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
       <c r="Q63" s="1"/>
+      <c r="R63" s="1"/>
+      <c r="S63" s="1"/>
     </row>
     <row r="64">
       <c r="A64" s="1"/>
@@ -3743,6 +4116,8 @@
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
+      <c r="R64" s="1"/>
+      <c r="S64" s="1"/>
     </row>
     <row r="65">
       <c r="A65" s="1"/>
@@ -3762,6 +4137,8 @@
       <c r="O65" s="1"/>
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
+      <c r="R65" s="1"/>
+      <c r="S65" s="1"/>
     </row>
     <row r="66">
       <c r="A66" s="1"/>
@@ -3781,6 +4158,8 @@
       <c r="O66" s="1"/>
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
+      <c r="R66" s="1"/>
+      <c r="S66" s="1"/>
     </row>
     <row r="67">
       <c r="A67" s="1"/>
@@ -3800,6 +4179,8 @@
       <c r="O67" s="1"/>
       <c r="P67" s="1"/>
       <c r="Q67" s="1"/>
+      <c r="R67" s="1"/>
+      <c r="S67" s="1"/>
     </row>
     <row r="68">
       <c r="A68" s="1"/>
@@ -3819,6 +4200,8 @@
       <c r="O68" s="1"/>
       <c r="P68" s="1"/>
       <c r="Q68" s="1"/>
+      <c r="R68" s="1"/>
+      <c r="S68" s="1"/>
     </row>
     <row r="69">
       <c r="A69" s="1"/>
@@ -3838,6 +4221,8 @@
       <c r="O69" s="1"/>
       <c r="P69" s="1"/>
       <c r="Q69" s="1"/>
+      <c r="R69" s="1"/>
+      <c r="S69" s="1"/>
     </row>
     <row r="70">
       <c r="A70" s="1"/>
@@ -3857,6 +4242,8 @@
       <c r="O70" s="1"/>
       <c r="P70" s="1"/>
       <c r="Q70" s="1"/>
+      <c r="R70" s="1"/>
+      <c r="S70" s="1"/>
     </row>
     <row r="71">
       <c r="A71" s="1"/>
@@ -3876,6 +4263,8 @@
       <c r="O71" s="1"/>
       <c r="P71" s="1"/>
       <c r="Q71" s="1"/>
+      <c r="R71" s="1"/>
+      <c r="S71" s="1"/>
     </row>
     <row r="72">
       <c r="A72" s="1"/>
@@ -3895,6 +4284,8 @@
       <c r="O72" s="1"/>
       <c r="P72" s="1"/>
       <c r="Q72" s="1"/>
+      <c r="R72" s="1"/>
+      <c r="S72" s="1"/>
     </row>
     <row r="73">
       <c r="A73" s="1"/>
@@ -3914,6 +4305,8 @@
       <c r="O73" s="1"/>
       <c r="P73" s="1"/>
       <c r="Q73" s="1"/>
+      <c r="R73" s="1"/>
+      <c r="S73" s="1"/>
     </row>
     <row r="74">
       <c r="A74" s="1"/>
@@ -3933,6 +4326,8 @@
       <c r="O74" s="1"/>
       <c r="P74" s="1"/>
       <c r="Q74" s="1"/>
+      <c r="R74" s="1"/>
+      <c r="S74" s="1"/>
     </row>
     <row r="75">
       <c r="A75" s="1"/>
@@ -3952,6 +4347,8 @@
       <c r="O75" s="1"/>
       <c r="P75" s="1"/>
       <c r="Q75" s="1"/>
+      <c r="R75" s="1"/>
+      <c r="S75" s="1"/>
     </row>
     <row r="76">
       <c r="A76" s="1"/>
@@ -3971,6 +4368,8 @@
       <c r="O76" s="1"/>
       <c r="P76" s="1"/>
       <c r="Q76" s="1"/>
+      <c r="R76" s="1"/>
+      <c r="S76" s="1"/>
     </row>
     <row r="77">
       <c r="A77" s="1"/>
@@ -3990,6 +4389,8 @@
       <c r="O77" s="1"/>
       <c r="P77" s="1"/>
       <c r="Q77" s="1"/>
+      <c r="R77" s="1"/>
+      <c r="S77" s="1"/>
     </row>
     <row r="78">
       <c r="A78" s="1"/>
@@ -4009,6 +4410,8 @@
       <c r="O78" s="1"/>
       <c r="P78" s="1"/>
       <c r="Q78" s="1"/>
+      <c r="R78" s="1"/>
+      <c r="S78" s="1"/>
     </row>
     <row r="79">
       <c r="A79" s="1"/>
@@ -4028,6 +4431,8 @@
       <c r="O79" s="1"/>
       <c r="P79" s="1"/>
       <c r="Q79" s="1"/>
+      <c r="R79" s="1"/>
+      <c r="S79" s="1"/>
     </row>
     <row r="80">
       <c r="A80" s="1"/>
@@ -4047,6 +4452,8 @@
       <c r="O80" s="1"/>
       <c r="P80" s="1"/>
       <c r="Q80" s="1"/>
+      <c r="R80" s="1"/>
+      <c r="S80" s="1"/>
     </row>
     <row r="81">
       <c r="A81" s="1"/>
@@ -4066,6 +4473,8 @@
       <c r="O81" s="1"/>
       <c r="P81" s="1"/>
       <c r="Q81" s="1"/>
+      <c r="R81" s="1"/>
+      <c r="S81" s="1"/>
     </row>
     <row r="82">
       <c r="A82" s="1"/>
@@ -4085,6 +4494,8 @@
       <c r="O82" s="1"/>
       <c r="P82" s="1"/>
       <c r="Q82" s="1"/>
+      <c r="R82" s="1"/>
+      <c r="S82" s="1"/>
     </row>
     <row r="83">
       <c r="A83" s="1"/>
@@ -4104,6 +4515,8 @@
       <c r="O83" s="1"/>
       <c r="P83" s="1"/>
       <c r="Q83" s="1"/>
+      <c r="R83" s="1"/>
+      <c r="S83" s="1"/>
     </row>
     <row r="84">
       <c r="A84" s="1"/>
@@ -4123,6 +4536,8 @@
       <c r="O84" s="1"/>
       <c r="P84" s="1"/>
       <c r="Q84" s="1"/>
+      <c r="R84" s="1"/>
+      <c r="S84" s="1"/>
     </row>
     <row r="85">
       <c r="A85" s="1"/>
@@ -4142,6 +4557,8 @@
       <c r="O85" s="1"/>
       <c r="P85" s="1"/>
       <c r="Q85" s="1"/>
+      <c r="R85" s="1"/>
+      <c r="S85" s="1"/>
     </row>
     <row r="86">
       <c r="A86" s="1"/>
@@ -4161,6 +4578,8 @@
       <c r="O86" s="1"/>
       <c r="P86" s="1"/>
       <c r="Q86" s="1"/>
+      <c r="R86" s="1"/>
+      <c r="S86" s="1"/>
     </row>
     <row r="87">
       <c r="A87" s="1"/>
@@ -4180,6 +4599,8 @@
       <c r="O87" s="1"/>
       <c r="P87" s="1"/>
       <c r="Q87" s="1"/>
+      <c r="R87" s="1"/>
+      <c r="S87" s="1"/>
     </row>
     <row r="88">
       <c r="A88" s="1"/>
@@ -4199,6 +4620,8 @@
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
+      <c r="R88" s="1"/>
+      <c r="S88" s="1"/>
     </row>
     <row r="89">
       <c r="A89" s="1"/>
@@ -4218,6 +4641,8 @@
       <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
+      <c r="R89" s="1"/>
+      <c r="S89" s="1"/>
     </row>
     <row r="90">
       <c r="A90" s="1"/>
@@ -4237,6 +4662,8 @@
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
+      <c r="R90" s="1"/>
+      <c r="S90" s="1"/>
     </row>
     <row r="91">
       <c r="A91" s="1"/>
@@ -4256,6 +4683,8 @@
       <c r="O91" s="1"/>
       <c r="P91" s="1"/>
       <c r="Q91" s="1"/>
+      <c r="R91" s="1"/>
+      <c r="S91" s="1"/>
     </row>
     <row r="92">
       <c r="A92" s="1"/>
@@ -4275,6 +4704,8 @@
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
+      <c r="R92" s="1"/>
+      <c r="S92" s="1"/>
     </row>
     <row r="93">
       <c r="A93" s="1"/>
@@ -4294,6 +4725,8 @@
       <c r="O93" s="1"/>
       <c r="P93" s="1"/>
       <c r="Q93" s="1"/>
+      <c r="R93" s="1"/>
+      <c r="S93" s="1"/>
     </row>
     <row r="94">
       <c r="A94" s="1"/>
@@ -4313,6 +4746,8 @@
       <c r="O94" s="1"/>
       <c r="P94" s="1"/>
       <c r="Q94" s="1"/>
+      <c r="R94" s="1"/>
+      <c r="S94" s="1"/>
     </row>
     <row r="95">
       <c r="A95" s="1"/>
@@ -4332,6 +4767,8 @@
       <c r="O95" s="1"/>
       <c r="P95" s="1"/>
       <c r="Q95" s="1"/>
+      <c r="R95" s="1"/>
+      <c r="S95" s="1"/>
     </row>
     <row r="96">
       <c r="A96" s="1"/>
@@ -4351,6 +4788,8 @@
       <c r="O96" s="1"/>
       <c r="P96" s="1"/>
       <c r="Q96" s="1"/>
+      <c r="R96" s="1"/>
+      <c r="S96" s="1"/>
     </row>
     <row r="97">
       <c r="A97" s="1"/>
@@ -4370,6 +4809,8 @@
       <c r="O97" s="1"/>
       <c r="P97" s="1"/>
       <c r="Q97" s="1"/>
+      <c r="R97" s="1"/>
+      <c r="S97" s="1"/>
     </row>
     <row r="98">
       <c r="A98" s="1"/>
@@ -4389,6 +4830,8 @@
       <c r="O98" s="1"/>
       <c r="P98" s="1"/>
       <c r="Q98" s="1"/>
+      <c r="R98" s="1"/>
+      <c r="S98" s="1"/>
     </row>
     <row r="99">
       <c r="A99" s="1"/>
@@ -4408,6 +4851,8 @@
       <c r="O99" s="1"/>
       <c r="P99" s="1"/>
       <c r="Q99" s="1"/>
+      <c r="R99" s="1"/>
+      <c r="S99" s="1"/>
     </row>
     <row r="100">
       <c r="A100" s="1"/>
@@ -4427,6 +4872,8 @@
       <c r="O100" s="1"/>
       <c r="P100" s="1"/>
       <c r="Q100" s="1"/>
+      <c r="R100" s="1"/>
+      <c r="S100" s="1"/>
     </row>
     <row r="101">
       <c r="A101" s="1"/>
@@ -4446,6 +4893,8 @@
       <c r="O101" s="1"/>
       <c r="P101" s="1"/>
       <c r="Q101" s="1"/>
+      <c r="R101" s="1"/>
+      <c r="S101" s="1"/>
     </row>
     <row r="102">
       <c r="A102" s="1"/>
@@ -4465,6 +4914,8 @@
       <c r="O102" s="1"/>
       <c r="P102" s="1"/>
       <c r="Q102" s="1"/>
+      <c r="R102" s="1"/>
+      <c r="S102" s="1"/>
     </row>
     <row r="103">
       <c r="A103" s="1"/>
@@ -4484,6 +4935,8 @@
       <c r="O103" s="1"/>
       <c r="P103" s="1"/>
       <c r="Q103" s="1"/>
+      <c r="R103" s="1"/>
+      <c r="S103" s="1"/>
     </row>
     <row r="104">
       <c r="A104" s="1"/>
@@ -4503,6 +4956,8 @@
       <c r="O104" s="1"/>
       <c r="P104" s="1"/>
       <c r="Q104" s="1"/>
+      <c r="R104" s="1"/>
+      <c r="S104" s="1"/>
     </row>
     <row r="105">
       <c r="A105" s="1"/>
@@ -4522,6 +4977,8 @@
       <c r="O105" s="1"/>
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
+      <c r="R105" s="1"/>
+      <c r="S105" s="1"/>
     </row>
     <row r="106">
       <c r="A106" s="1"/>
@@ -4541,6 +4998,8 @@
       <c r="O106" s="1"/>
       <c r="P106" s="1"/>
       <c r="Q106" s="1"/>
+      <c r="R106" s="1"/>
+      <c r="S106" s="1"/>
     </row>
     <row r="107">
       <c r="A107" s="1"/>
@@ -4560,6 +5019,8 @@
       <c r="O107" s="1"/>
       <c r="P107" s="1"/>
       <c r="Q107" s="1"/>
+      <c r="R107" s="1"/>
+      <c r="S107" s="1"/>
     </row>
     <row r="108">
       <c r="A108" s="1"/>
@@ -4579,6 +5040,8 @@
       <c r="O108" s="1"/>
       <c r="P108" s="1"/>
       <c r="Q108" s="1"/>
+      <c r="R108" s="1"/>
+      <c r="S108" s="1"/>
     </row>
     <row r="109">
       <c r="A109" s="1"/>
@@ -4598,6 +5061,8 @@
       <c r="O109" s="1"/>
       <c r="P109" s="1"/>
       <c r="Q109" s="1"/>
+      <c r="R109" s="1"/>
+      <c r="S109" s="1"/>
     </row>
     <row r="110">
       <c r="A110" s="1"/>
@@ -4617,6 +5082,8 @@
       <c r="O110" s="1"/>
       <c r="P110" s="1"/>
       <c r="Q110" s="1"/>
+      <c r="R110" s="1"/>
+      <c r="S110" s="1"/>
     </row>
     <row r="111">
       <c r="A111" s="1"/>
@@ -4636,6 +5103,8 @@
       <c r="O111" s="1"/>
       <c r="P111" s="1"/>
       <c r="Q111" s="1"/>
+      <c r="R111" s="1"/>
+      <c r="S111" s="1"/>
     </row>
     <row r="112">
       <c r="A112" s="1"/>
@@ -4655,6 +5124,8 @@
       <c r="O112" s="1"/>
       <c r="P112" s="1"/>
       <c r="Q112" s="1"/>
+      <c r="R112" s="1"/>
+      <c r="S112" s="1"/>
     </row>
     <row r="113">
       <c r="A113" s="1"/>
@@ -4674,6 +5145,8 @@
       <c r="O113" s="1"/>
       <c r="P113" s="1"/>
       <c r="Q113" s="1"/>
+      <c r="R113" s="1"/>
+      <c r="S113" s="1"/>
     </row>
     <row r="114">
       <c r="A114" s="1"/>
@@ -4693,6 +5166,8 @@
       <c r="O114" s="1"/>
       <c r="P114" s="1"/>
       <c r="Q114" s="1"/>
+      <c r="R114" s="1"/>
+      <c r="S114" s="1"/>
     </row>
     <row r="115">
       <c r="A115" s="1"/>
@@ -4712,6 +5187,8 @@
       <c r="O115" s="1"/>
       <c r="P115" s="1"/>
       <c r="Q115" s="1"/>
+      <c r="R115" s="1"/>
+      <c r="S115" s="1"/>
     </row>
     <row r="116">
       <c r="A116" s="1"/>
@@ -4731,6 +5208,8 @@
       <c r="O116" s="1"/>
       <c r="P116" s="1"/>
       <c r="Q116" s="1"/>
+      <c r="R116" s="1"/>
+      <c r="S116" s="1"/>
     </row>
     <row r="117">
       <c r="A117" s="1"/>
@@ -4750,6 +5229,8 @@
       <c r="O117" s="1"/>
       <c r="P117" s="1"/>
       <c r="Q117" s="1"/>
+      <c r="R117" s="1"/>
+      <c r="S117" s="1"/>
     </row>
     <row r="118">
       <c r="A118" s="1"/>
@@ -4769,6 +5250,8 @@
       <c r="O118" s="1"/>
       <c r="P118" s="1"/>
       <c r="Q118" s="1"/>
+      <c r="R118" s="1"/>
+      <c r="S118" s="1"/>
     </row>
     <row r="119">
       <c r="A119" s="1"/>
@@ -4788,6 +5271,8 @@
       <c r="O119" s="1"/>
       <c r="P119" s="1"/>
       <c r="Q119" s="1"/>
+      <c r="R119" s="1"/>
+      <c r="S119" s="1"/>
     </row>
     <row r="120">
       <c r="A120" s="1"/>
@@ -4807,6 +5292,8 @@
       <c r="O120" s="1"/>
       <c r="P120" s="1"/>
       <c r="Q120" s="1"/>
+      <c r="R120" s="1"/>
+      <c r="S120" s="1"/>
     </row>
     <row r="121">
       <c r="A121" s="1"/>
@@ -4826,6 +5313,8 @@
       <c r="O121" s="1"/>
       <c r="P121" s="1"/>
       <c r="Q121" s="1"/>
+      <c r="R121" s="1"/>
+      <c r="S121" s="1"/>
     </row>
     <row r="122">
       <c r="A122" s="1"/>
@@ -4845,6 +5334,8 @@
       <c r="O122" s="1"/>
       <c r="P122" s="1"/>
       <c r="Q122" s="1"/>
+      <c r="R122" s="1"/>
+      <c r="S122" s="1"/>
     </row>
     <row r="123">
       <c r="A123" s="1"/>
@@ -4864,6 +5355,8 @@
       <c r="O123" s="1"/>
       <c r="P123" s="1"/>
       <c r="Q123" s="1"/>
+      <c r="R123" s="1"/>
+      <c r="S123" s="1"/>
     </row>
     <row r="124">
       <c r="A124" s="1"/>
@@ -4883,6 +5376,8 @@
       <c r="O124" s="1"/>
       <c r="P124" s="1"/>
       <c r="Q124" s="1"/>
+      <c r="R124" s="1"/>
+      <c r="S124" s="1"/>
     </row>
     <row r="125">
       <c r="A125" s="1"/>
@@ -4902,6 +5397,8 @@
       <c r="O125" s="1"/>
       <c r="P125" s="1"/>
       <c r="Q125" s="1"/>
+      <c r="R125" s="1"/>
+      <c r="S125" s="1"/>
     </row>
     <row r="126">
       <c r="A126" s="1"/>
@@ -4921,6 +5418,8 @@
       <c r="O126" s="1"/>
       <c r="P126" s="1"/>
       <c r="Q126" s="1"/>
+      <c r="R126" s="1"/>
+      <c r="S126" s="1"/>
     </row>
     <row r="127">
       <c r="A127" s="1"/>
@@ -4940,6 +5439,8 @@
       <c r="O127" s="1"/>
       <c r="P127" s="1"/>
       <c r="Q127" s="1"/>
+      <c r="R127" s="1"/>
+      <c r="S127" s="1"/>
     </row>
     <row r="128">
       <c r="A128" s="1"/>
@@ -4959,6 +5460,8 @@
       <c r="O128" s="1"/>
       <c r="P128" s="1"/>
       <c r="Q128" s="1"/>
+      <c r="R128" s="1"/>
+      <c r="S128" s="1"/>
     </row>
     <row r="129">
       <c r="A129" s="1"/>
@@ -4978,6 +5481,8 @@
       <c r="O129" s="1"/>
       <c r="P129" s="1"/>
       <c r="Q129" s="1"/>
+      <c r="R129" s="1"/>
+      <c r="S129" s="1"/>
     </row>
     <row r="130">
       <c r="A130" s="1"/>
@@ -4997,6 +5502,8 @@
       <c r="O130" s="1"/>
       <c r="P130" s="1"/>
       <c r="Q130" s="1"/>
+      <c r="R130" s="1"/>
+      <c r="S130" s="1"/>
     </row>
     <row r="131">
       <c r="A131" s="1"/>
@@ -5016,6 +5523,8 @@
       <c r="O131" s="1"/>
       <c r="P131" s="1"/>
       <c r="Q131" s="1"/>
+      <c r="R131" s="1"/>
+      <c r="S131" s="1"/>
     </row>
     <row r="132">
       <c r="A132" s="1"/>
@@ -5035,6 +5544,8 @@
       <c r="O132" s="1"/>
       <c r="P132" s="1"/>
       <c r="Q132" s="1"/>
+      <c r="R132" s="1"/>
+      <c r="S132" s="1"/>
     </row>
     <row r="133">
       <c r="A133" s="1"/>
@@ -5054,6 +5565,8 @@
       <c r="O133" s="1"/>
       <c r="P133" s="1"/>
       <c r="Q133" s="1"/>
+      <c r="R133" s="1"/>
+      <c r="S133" s="1"/>
     </row>
     <row r="134">
       <c r="A134" s="1"/>
@@ -5073,6 +5586,8 @@
       <c r="O134" s="1"/>
       <c r="P134" s="1"/>
       <c r="Q134" s="1"/>
+      <c r="R134" s="1"/>
+      <c r="S134" s="1"/>
     </row>
     <row r="135">
       <c r="A135" s="1"/>
@@ -5092,6 +5607,8 @@
       <c r="O135" s="1"/>
       <c r="P135" s="1"/>
       <c r="Q135" s="1"/>
+      <c r="R135" s="1"/>
+      <c r="S135" s="1"/>
     </row>
     <row r="136">
       <c r="A136" s="1"/>
@@ -5111,6 +5628,8 @@
       <c r="O136" s="1"/>
       <c r="P136" s="1"/>
       <c r="Q136" s="1"/>
+      <c r="R136" s="1"/>
+      <c r="S136" s="1"/>
     </row>
     <row r="137">
       <c r="A137" s="1"/>
@@ -5130,6 +5649,8 @@
       <c r="O137" s="1"/>
       <c r="P137" s="1"/>
       <c r="Q137" s="1"/>
+      <c r="R137" s="1"/>
+      <c r="S137" s="1"/>
     </row>
     <row r="138">
       <c r="A138" s="1"/>
@@ -5149,6 +5670,8 @@
       <c r="O138" s="1"/>
       <c r="P138" s="1"/>
       <c r="Q138" s="1"/>
+      <c r="R138" s="1"/>
+      <c r="S138" s="1"/>
     </row>
     <row r="139">
       <c r="A139" s="1"/>
@@ -5168,6 +5691,8 @@
       <c r="O139" s="1"/>
       <c r="P139" s="1"/>
       <c r="Q139" s="1"/>
+      <c r="R139" s="1"/>
+      <c r="S139" s="1"/>
     </row>
     <row r="140">
       <c r="A140" s="1"/>
@@ -5187,6 +5712,8 @@
       <c r="O140" s="1"/>
       <c r="P140" s="1"/>
       <c r="Q140" s="1"/>
+      <c r="R140" s="1"/>
+      <c r="S140" s="1"/>
     </row>
     <row r="141">
       <c r="A141" s="1"/>
@@ -5206,6 +5733,8 @@
       <c r="O141" s="1"/>
       <c r="P141" s="1"/>
       <c r="Q141" s="1"/>
+      <c r="R141" s="1"/>
+      <c r="S141" s="1"/>
     </row>
     <row r="142">
       <c r="A142" s="1"/>
@@ -5225,6 +5754,8 @@
       <c r="O142" s="1"/>
       <c r="P142" s="1"/>
       <c r="Q142" s="1"/>
+      <c r="R142" s="1"/>
+      <c r="S142" s="1"/>
     </row>
     <row r="143">
       <c r="A143" s="1"/>
@@ -5244,6 +5775,8 @@
       <c r="O143" s="1"/>
       <c r="P143" s="1"/>
       <c r="Q143" s="1"/>
+      <c r="R143" s="1"/>
+      <c r="S143" s="1"/>
     </row>
     <row r="144">
       <c r="A144" s="1"/>
@@ -5263,6 +5796,8 @@
       <c r="O144" s="1"/>
       <c r="P144" s="1"/>
       <c r="Q144" s="1"/>
+      <c r="R144" s="1"/>
+      <c r="S144" s="1"/>
     </row>
     <row r="145">
       <c r="A145" s="1"/>
@@ -5282,6 +5817,8 @@
       <c r="O145" s="1"/>
       <c r="P145" s="1"/>
       <c r="Q145" s="1"/>
+      <c r="R145" s="1"/>
+      <c r="S145" s="1"/>
     </row>
     <row r="146">
       <c r="A146" s="1"/>
@@ -5301,6 +5838,8 @@
       <c r="O146" s="1"/>
       <c r="P146" s="1"/>
       <c r="Q146" s="1"/>
+      <c r="R146" s="1"/>
+      <c r="S146" s="1"/>
     </row>
     <row r="147">
       <c r="A147" s="1"/>
@@ -5320,6 +5859,8 @@
       <c r="O147" s="1"/>
       <c r="P147" s="1"/>
       <c r="Q147" s="1"/>
+      <c r="R147" s="1"/>
+      <c r="S147" s="1"/>
     </row>
     <row r="148">
       <c r="A148" s="1"/>
@@ -5339,6 +5880,8 @@
       <c r="O148" s="1"/>
       <c r="P148" s="1"/>
       <c r="Q148" s="1"/>
+      <c r="R148" s="1"/>
+      <c r="S148" s="1"/>
     </row>
     <row r="149">
       <c r="A149" s="1"/>
@@ -5358,6 +5901,8 @@
       <c r="O149" s="1"/>
       <c r="P149" s="1"/>
       <c r="Q149" s="1"/>
+      <c r="R149" s="1"/>
+      <c r="S149" s="1"/>
     </row>
     <row r="150">
       <c r="A150" s="1"/>
@@ -5377,6 +5922,8 @@
       <c r="O150" s="1"/>
       <c r="P150" s="1"/>
       <c r="Q150" s="1"/>
+      <c r="R150" s="1"/>
+      <c r="S150" s="1"/>
     </row>
     <row r="151">
       <c r="A151" s="1"/>
@@ -5396,6 +5943,8 @@
       <c r="O151" s="1"/>
       <c r="P151" s="1"/>
       <c r="Q151" s="1"/>
+      <c r="R151" s="1"/>
+      <c r="S151" s="1"/>
     </row>
     <row r="152">
       <c r="A152" s="1"/>
@@ -5415,6 +5964,8 @@
       <c r="O152" s="1"/>
       <c r="P152" s="1"/>
       <c r="Q152" s="1"/>
+      <c r="R152" s="1"/>
+      <c r="S152" s="1"/>
     </row>
     <row r="153">
       <c r="A153" s="1"/>
@@ -5434,6 +5985,8 @@
       <c r="O153" s="1"/>
       <c r="P153" s="1"/>
       <c r="Q153" s="1"/>
+      <c r="R153" s="1"/>
+      <c r="S153" s="1"/>
     </row>
     <row r="154">
       <c r="A154" s="1"/>
@@ -5453,6 +6006,8 @@
       <c r="O154" s="1"/>
       <c r="P154" s="1"/>
       <c r="Q154" s="1"/>
+      <c r="R154" s="1"/>
+      <c r="S154" s="1"/>
     </row>
     <row r="155">
       <c r="A155" s="1"/>
@@ -5472,6 +6027,8 @@
       <c r="O155" s="1"/>
       <c r="P155" s="1"/>
       <c r="Q155" s="1"/>
+      <c r="R155" s="1"/>
+      <c r="S155" s="1"/>
     </row>
     <row r="156">
       <c r="A156" s="1"/>
@@ -5491,6 +6048,8 @@
       <c r="O156" s="1"/>
       <c r="P156" s="1"/>
       <c r="Q156" s="1"/>
+      <c r="R156" s="1"/>
+      <c r="S156" s="1"/>
     </row>
     <row r="157">
       <c r="A157" s="1"/>
@@ -5510,6 +6069,8 @@
       <c r="O157" s="1"/>
       <c r="P157" s="1"/>
       <c r="Q157" s="1"/>
+      <c r="R157" s="1"/>
+      <c r="S157" s="1"/>
     </row>
     <row r="158">
       <c r="A158" s="1"/>
@@ -5529,6 +6090,8 @@
       <c r="O158" s="1"/>
       <c r="P158" s="1"/>
       <c r="Q158" s="1"/>
+      <c r="R158" s="1"/>
+      <c r="S158" s="1"/>
     </row>
     <row r="159">
       <c r="A159" s="1"/>
@@ -5548,6 +6111,8 @@
       <c r="O159" s="1"/>
       <c r="P159" s="1"/>
       <c r="Q159" s="1"/>
+      <c r="R159" s="1"/>
+      <c r="S159" s="1"/>
     </row>
     <row r="160">
       <c r="A160" s="1"/>
@@ -5567,6 +6132,8 @@
       <c r="O160" s="1"/>
       <c r="P160" s="1"/>
       <c r="Q160" s="1"/>
+      <c r="R160" s="1"/>
+      <c r="S160" s="1"/>
     </row>
     <row r="161">
       <c r="A161" s="1"/>
@@ -5586,6 +6153,8 @@
       <c r="O161" s="1"/>
       <c r="P161" s="1"/>
       <c r="Q161" s="1"/>
+      <c r="R161" s="1"/>
+      <c r="S161" s="1"/>
     </row>
     <row r="162">
       <c r="A162" s="1"/>
@@ -5605,6 +6174,8 @@
       <c r="O162" s="1"/>
       <c r="P162" s="1"/>
       <c r="Q162" s="1"/>
+      <c r="R162" s="1"/>
+      <c r="S162" s="1"/>
     </row>
     <row r="163">
       <c r="A163" s="1"/>
@@ -5624,6 +6195,8 @@
       <c r="O163" s="1"/>
       <c r="P163" s="1"/>
       <c r="Q163" s="1"/>
+      <c r="R163" s="1"/>
+      <c r="S163" s="1"/>
     </row>
     <row r="164">
       <c r="A164" s="1"/>
@@ -5643,6 +6216,8 @@
       <c r="O164" s="1"/>
       <c r="P164" s="1"/>
       <c r="Q164" s="1"/>
+      <c r="R164" s="1"/>
+      <c r="S164" s="1"/>
     </row>
     <row r="165">
       <c r="A165" s="1"/>
@@ -5662,6 +6237,8 @@
       <c r="O165" s="1"/>
       <c r="P165" s="1"/>
       <c r="Q165" s="1"/>
+      <c r="R165" s="1"/>
+      <c r="S165" s="1"/>
     </row>
     <row r="166">
       <c r="A166" s="1"/>
@@ -5681,6 +6258,8 @@
       <c r="O166" s="1"/>
       <c r="P166" s="1"/>
       <c r="Q166" s="1"/>
+      <c r="R166" s="1"/>
+      <c r="S166" s="1"/>
     </row>
     <row r="167">
       <c r="A167" s="1"/>
@@ -5700,6 +6279,8 @@
       <c r="O167" s="1"/>
       <c r="P167" s="1"/>
       <c r="Q167" s="1"/>
+      <c r="R167" s="1"/>
+      <c r="S167" s="1"/>
     </row>
     <row r="168">
       <c r="A168" s="1"/>
@@ -5719,6 +6300,8 @@
       <c r="O168" s="1"/>
       <c r="P168" s="1"/>
       <c r="Q168" s="1"/>
+      <c r="R168" s="1"/>
+      <c r="S168" s="1"/>
     </row>
     <row r="169">
       <c r="A169" s="1"/>
@@ -5738,6 +6321,8 @@
       <c r="O169" s="1"/>
       <c r="P169" s="1"/>
       <c r="Q169" s="1"/>
+      <c r="R169" s="1"/>
+      <c r="S169" s="1"/>
     </row>
     <row r="170">
       <c r="A170" s="1"/>
@@ -5757,6 +6342,8 @@
       <c r="O170" s="1"/>
       <c r="P170" s="1"/>
       <c r="Q170" s="1"/>
+      <c r="R170" s="1"/>
+      <c r="S170" s="1"/>
     </row>
     <row r="171">
       <c r="A171" s="1"/>
@@ -5776,6 +6363,8 @@
       <c r="O171" s="1"/>
       <c r="P171" s="1"/>
       <c r="Q171" s="1"/>
+      <c r="R171" s="1"/>
+      <c r="S171" s="1"/>
     </row>
     <row r="172">
       <c r="A172" s="1"/>
@@ -5795,6 +6384,8 @@
       <c r="O172" s="1"/>
       <c r="P172" s="1"/>
       <c r="Q172" s="1"/>
+      <c r="R172" s="1"/>
+      <c r="S172" s="1"/>
     </row>
     <row r="173">
       <c r="A173" s="1"/>
@@ -5814,6 +6405,8 @@
       <c r="O173" s="1"/>
       <c r="P173" s="1"/>
       <c r="Q173" s="1"/>
+      <c r="R173" s="1"/>
+      <c r="S173" s="1"/>
     </row>
     <row r="174">
       <c r="A174" s="1"/>
@@ -5833,6 +6426,8 @@
       <c r="O174" s="1"/>
       <c r="P174" s="1"/>
       <c r="Q174" s="1"/>
+      <c r="R174" s="1"/>
+      <c r="S174" s="1"/>
     </row>
     <row r="175">
       <c r="A175" s="1"/>
@@ -5852,6 +6447,8 @@
       <c r="O175" s="1"/>
       <c r="P175" s="1"/>
       <c r="Q175" s="1"/>
+      <c r="R175" s="1"/>
+      <c r="S175" s="1"/>
     </row>
     <row r="176">
       <c r="A176" s="1"/>
@@ -5871,6 +6468,8 @@
       <c r="O176" s="1"/>
       <c r="P176" s="1"/>
       <c r="Q176" s="1"/>
+      <c r="R176" s="1"/>
+      <c r="S176" s="1"/>
     </row>
     <row r="177">
       <c r="A177" s="1"/>
@@ -5890,6 +6489,8 @@
       <c r="O177" s="1"/>
       <c r="P177" s="1"/>
       <c r="Q177" s="1"/>
+      <c r="R177" s="1"/>
+      <c r="S177" s="1"/>
     </row>
     <row r="178">
       <c r="A178" s="1"/>
@@ -5909,6 +6510,8 @@
       <c r="O178" s="1"/>
       <c r="P178" s="1"/>
       <c r="Q178" s="1"/>
+      <c r="R178" s="1"/>
+      <c r="S178" s="1"/>
     </row>
     <row r="179">
       <c r="A179" s="1"/>
@@ -5928,6 +6531,8 @@
       <c r="O179" s="1"/>
       <c r="P179" s="1"/>
       <c r="Q179" s="1"/>
+      <c r="R179" s="1"/>
+      <c r="S179" s="1"/>
     </row>
     <row r="180">
       <c r="A180" s="1"/>
@@ -5947,6 +6552,8 @@
       <c r="O180" s="1"/>
       <c r="P180" s="1"/>
       <c r="Q180" s="1"/>
+      <c r="R180" s="1"/>
+      <c r="S180" s="1"/>
     </row>
     <row r="181">
       <c r="A181" s="1"/>
@@ -5966,6 +6573,8 @@
       <c r="O181" s="1"/>
       <c r="P181" s="1"/>
       <c r="Q181" s="1"/>
+      <c r="R181" s="1"/>
+      <c r="S181" s="1"/>
     </row>
     <row r="182">
       <c r="A182" s="1"/>
@@ -5985,6 +6594,8 @@
       <c r="O182" s="1"/>
       <c r="P182" s="1"/>
       <c r="Q182" s="1"/>
+      <c r="R182" s="1"/>
+      <c r="S182" s="1"/>
     </row>
     <row r="183">
       <c r="A183" s="1"/>
@@ -6004,6 +6615,8 @@
       <c r="O183" s="1"/>
       <c r="P183" s="1"/>
       <c r="Q183" s="1"/>
+      <c r="R183" s="1"/>
+      <c r="S183" s="1"/>
     </row>
     <row r="184">
       <c r="A184" s="1"/>
@@ -6023,6 +6636,8 @@
       <c r="O184" s="1"/>
       <c r="P184" s="1"/>
       <c r="Q184" s="1"/>
+      <c r="R184" s="1"/>
+      <c r="S184" s="1"/>
     </row>
     <row r="185">
       <c r="A185" s="1"/>
@@ -6042,6 +6657,8 @@
       <c r="O185" s="1"/>
       <c r="P185" s="1"/>
       <c r="Q185" s="1"/>
+      <c r="R185" s="1"/>
+      <c r="S185" s="1"/>
     </row>
     <row r="186">
       <c r="A186" s="1"/>
@@ -6061,6 +6678,8 @@
       <c r="O186" s="1"/>
       <c r="P186" s="1"/>
       <c r="Q186" s="1"/>
+      <c r="R186" s="1"/>
+      <c r="S186" s="1"/>
     </row>
     <row r="187">
       <c r="A187" s="1"/>
@@ -6080,6 +6699,8 @@
       <c r="O187" s="1"/>
       <c r="P187" s="1"/>
       <c r="Q187" s="1"/>
+      <c r="R187" s="1"/>
+      <c r="S187" s="1"/>
     </row>
     <row r="188">
       <c r="A188" s="1"/>
@@ -6099,6 +6720,8 @@
       <c r="O188" s="1"/>
       <c r="P188" s="1"/>
       <c r="Q188" s="1"/>
+      <c r="R188" s="1"/>
+      <c r="S188" s="1"/>
     </row>
     <row r="189">
       <c r="A189" s="1"/>
@@ -6118,6 +6741,8 @@
       <c r="O189" s="1"/>
       <c r="P189" s="1"/>
       <c r="Q189" s="1"/>
+      <c r="R189" s="1"/>
+      <c r="S189" s="1"/>
     </row>
     <row r="190">
       <c r="A190" s="1"/>
@@ -6137,6 +6762,8 @@
       <c r="O190" s="1"/>
       <c r="P190" s="1"/>
       <c r="Q190" s="1"/>
+      <c r="R190" s="1"/>
+      <c r="S190" s="1"/>
     </row>
     <row r="191">
       <c r="A191" s="1"/>
@@ -6156,6 +6783,8 @@
       <c r="O191" s="1"/>
       <c r="P191" s="1"/>
       <c r="Q191" s="1"/>
+      <c r="R191" s="1"/>
+      <c r="S191" s="1"/>
     </row>
     <row r="192">
       <c r="A192" s="1"/>
@@ -6175,6 +6804,8 @@
       <c r="O192" s="1"/>
       <c r="P192" s="1"/>
       <c r="Q192" s="1"/>
+      <c r="R192" s="1"/>
+      <c r="S192" s="1"/>
     </row>
     <row r="193">
       <c r="A193" s="1"/>
@@ -6194,6 +6825,8 @@
       <c r="O193" s="1"/>
       <c r="P193" s="1"/>
       <c r="Q193" s="1"/>
+      <c r="R193" s="1"/>
+      <c r="S193" s="1"/>
     </row>
     <row r="194">
       <c r="A194" s="1"/>
@@ -6213,6 +6846,8 @@
       <c r="O194" s="1"/>
       <c r="P194" s="1"/>
       <c r="Q194" s="1"/>
+      <c r="R194" s="1"/>
+      <c r="S194" s="1"/>
     </row>
     <row r="195">
       <c r="A195" s="1"/>
@@ -6232,6 +6867,8 @@
       <c r="O195" s="1"/>
       <c r="P195" s="1"/>
       <c r="Q195" s="1"/>
+      <c r="R195" s="1"/>
+      <c r="S195" s="1"/>
     </row>
     <row r="196">
       <c r="A196" s="1"/>
@@ -6251,6 +6888,8 @@
       <c r="O196" s="1"/>
       <c r="P196" s="1"/>
       <c r="Q196" s="1"/>
+      <c r="R196" s="1"/>
+      <c r="S196" s="1"/>
     </row>
     <row r="197">
       <c r="A197" s="1"/>
@@ -6270,6 +6909,8 @@
       <c r="O197" s="1"/>
       <c r="P197" s="1"/>
       <c r="Q197" s="1"/>
+      <c r="R197" s="1"/>
+      <c r="S197" s="1"/>
     </row>
     <row r="198">
       <c r="A198" s="1"/>
@@ -6289,6 +6930,8 @@
       <c r="O198" s="1"/>
       <c r="P198" s="1"/>
       <c r="Q198" s="1"/>
+      <c r="R198" s="1"/>
+      <c r="S198" s="1"/>
     </row>
     <row r="199">
       <c r="A199" s="1"/>
@@ -6308,6 +6951,8 @@
       <c r="O199" s="1"/>
       <c r="P199" s="1"/>
       <c r="Q199" s="1"/>
+      <c r="R199" s="1"/>
+      <c r="S199" s="1"/>
     </row>
     <row r="200">
       <c r="A200" s="1"/>
@@ -6327,6 +6972,8 @@
       <c r="O200" s="1"/>
       <c r="P200" s="1"/>
       <c r="Q200" s="1"/>
+      <c r="R200" s="1"/>
+      <c r="S200" s="1"/>
     </row>
     <row r="201">
       <c r="A201" s="1"/>
@@ -6346,6 +6993,8 @@
       <c r="O201" s="1"/>
       <c r="P201" s="1"/>
       <c r="Q201" s="1"/>
+      <c r="R201" s="1"/>
+      <c r="S201" s="1"/>
     </row>
     <row r="202">
       <c r="A202" s="1"/>
@@ -6365,6 +7014,8 @@
       <c r="O202" s="1"/>
       <c r="P202" s="1"/>
       <c r="Q202" s="1"/>
+      <c r="R202" s="1"/>
+      <c r="S202" s="1"/>
     </row>
     <row r="203">
       <c r="A203" s="1"/>
@@ -6384,6 +7035,8 @@
       <c r="O203" s="1"/>
       <c r="P203" s="1"/>
       <c r="Q203" s="1"/>
+      <c r="R203" s="1"/>
+      <c r="S203" s="1"/>
     </row>
     <row r="204">
       <c r="A204" s="1"/>
@@ -6403,6 +7056,8 @@
       <c r="O204" s="1"/>
       <c r="P204" s="1"/>
       <c r="Q204" s="1"/>
+      <c r="R204" s="1"/>
+      <c r="S204" s="1"/>
     </row>
     <row r="205">
       <c r="A205" s="1"/>
@@ -6422,6 +7077,8 @@
       <c r="O205" s="1"/>
       <c r="P205" s="1"/>
       <c r="Q205" s="1"/>
+      <c r="R205" s="1"/>
+      <c r="S205" s="1"/>
     </row>
     <row r="206">
       <c r="A206" s="1"/>
@@ -6441,6 +7098,8 @@
       <c r="O206" s="1"/>
       <c r="P206" s="1"/>
       <c r="Q206" s="1"/>
+      <c r="R206" s="1"/>
+      <c r="S206" s="1"/>
     </row>
     <row r="207">
       <c r="A207" s="1"/>
@@ -6460,6 +7119,8 @@
       <c r="O207" s="1"/>
       <c r="P207" s="1"/>
       <c r="Q207" s="1"/>
+      <c r="R207" s="1"/>
+      <c r="S207" s="1"/>
     </row>
     <row r="208">
       <c r="A208" s="1"/>
@@ -6479,6 +7140,8 @@
       <c r="O208" s="1"/>
       <c r="P208" s="1"/>
       <c r="Q208" s="1"/>
+      <c r="R208" s="1"/>
+      <c r="S208" s="1"/>
     </row>
     <row r="209">
       <c r="A209" s="1"/>
@@ -6498,6 +7161,8 @@
       <c r="O209" s="1"/>
       <c r="P209" s="1"/>
       <c r="Q209" s="1"/>
+      <c r="R209" s="1"/>
+      <c r="S209" s="1"/>
     </row>
     <row r="210">
       <c r="A210" s="1"/>
@@ -6517,6 +7182,8 @@
       <c r="O210" s="1"/>
       <c r="P210" s="1"/>
       <c r="Q210" s="1"/>
+      <c r="R210" s="1"/>
+      <c r="S210" s="1"/>
     </row>
     <row r="211">
       <c r="A211" s="1"/>
@@ -6536,6 +7203,8 @@
       <c r="O211" s="1"/>
       <c r="P211" s="1"/>
       <c r="Q211" s="1"/>
+      <c r="R211" s="1"/>
+      <c r="S211" s="1"/>
     </row>
     <row r="212">
       <c r="A212" s="1"/>
@@ -6555,6 +7224,8 @@
       <c r="O212" s="1"/>
       <c r="P212" s="1"/>
       <c r="Q212" s="1"/>
+      <c r="R212" s="1"/>
+      <c r="S212" s="1"/>
     </row>
     <row r="213">
       <c r="A213" s="1"/>
@@ -6574,6 +7245,8 @@
       <c r="O213" s="1"/>
       <c r="P213" s="1"/>
       <c r="Q213" s="1"/>
+      <c r="R213" s="1"/>
+      <c r="S213" s="1"/>
     </row>
     <row r="214">
       <c r="A214" s="1"/>
@@ -6593,6 +7266,8 @@
       <c r="O214" s="1"/>
       <c r="P214" s="1"/>
       <c r="Q214" s="1"/>
+      <c r="R214" s="1"/>
+      <c r="S214" s="1"/>
     </row>
     <row r="215">
       <c r="A215" s="1"/>
@@ -6612,6 +7287,8 @@
       <c r="O215" s="1"/>
       <c r="P215" s="1"/>
       <c r="Q215" s="1"/>
+      <c r="R215" s="1"/>
+      <c r="S215" s="1"/>
     </row>
     <row r="216">
       <c r="A216" s="1"/>
@@ -6631,6 +7308,8 @@
       <c r="O216" s="1"/>
       <c r="P216" s="1"/>
       <c r="Q216" s="1"/>
+      <c r="R216" s="1"/>
+      <c r="S216" s="1"/>
     </row>
     <row r="217">
       <c r="A217" s="1"/>
@@ -6650,6 +7329,8 @@
       <c r="O217" s="1"/>
       <c r="P217" s="1"/>
       <c r="Q217" s="1"/>
+      <c r="R217" s="1"/>
+      <c r="S217" s="1"/>
     </row>
     <row r="218">
       <c r="A218" s="1"/>
@@ -6669,6 +7350,8 @@
       <c r="O218" s="1"/>
       <c r="P218" s="1"/>
       <c r="Q218" s="1"/>
+      <c r="R218" s="1"/>
+      <c r="S218" s="1"/>
     </row>
     <row r="219">
       <c r="A219" s="1"/>
@@ -6688,6 +7371,8 @@
       <c r="O219" s="1"/>
       <c r="P219" s="1"/>
       <c r="Q219" s="1"/>
+      <c r="R219" s="1"/>
+      <c r="S219" s="1"/>
     </row>
     <row r="220">
       <c r="A220" s="1"/>
@@ -6707,6 +7392,8 @@
       <c r="O220" s="1"/>
       <c r="P220" s="1"/>
       <c r="Q220" s="1"/>
+      <c r="R220" s="1"/>
+      <c r="S220" s="1"/>
     </row>
     <row r="221">
       <c r="A221" s="1"/>
@@ -6726,6 +7413,8 @@
       <c r="O221" s="1"/>
       <c r="P221" s="1"/>
       <c r="Q221" s="1"/>
+      <c r="R221" s="1"/>
+      <c r="S221" s="1"/>
     </row>
     <row r="222">
       <c r="A222" s="1"/>
@@ -6745,6 +7434,8 @@
       <c r="O222" s="1"/>
       <c r="P222" s="1"/>
       <c r="Q222" s="1"/>
+      <c r="R222" s="1"/>
+      <c r="S222" s="1"/>
     </row>
     <row r="223">
       <c r="A223" s="1"/>
@@ -6764,6 +7455,8 @@
       <c r="O223" s="1"/>
       <c r="P223" s="1"/>
       <c r="Q223" s="1"/>
+      <c r="R223" s="1"/>
+      <c r="S223" s="1"/>
     </row>
     <row r="224">
       <c r="A224" s="1"/>
@@ -6783,6 +7476,8 @@
       <c r="O224" s="1"/>
       <c r="P224" s="1"/>
       <c r="Q224" s="1"/>
+      <c r="R224" s="1"/>
+      <c r="S224" s="1"/>
     </row>
     <row r="225">
       <c r="A225" s="1"/>
@@ -6802,6 +7497,8 @@
       <c r="O225" s="1"/>
       <c r="P225" s="1"/>
       <c r="Q225" s="1"/>
+      <c r="R225" s="1"/>
+      <c r="S225" s="1"/>
     </row>
     <row r="226">
       <c r="A226" s="1"/>
@@ -6821,6 +7518,8 @@
       <c r="O226" s="1"/>
       <c r="P226" s="1"/>
       <c r="Q226" s="1"/>
+      <c r="R226" s="1"/>
+      <c r="S226" s="1"/>
     </row>
     <row r="227">
       <c r="A227" s="1"/>
@@ -6840,6 +7539,8 @@
       <c r="O227" s="1"/>
       <c r="P227" s="1"/>
       <c r="Q227" s="1"/>
+      <c r="R227" s="1"/>
+      <c r="S227" s="1"/>
     </row>
     <row r="228">
       <c r="A228" s="1"/>
@@ -6859,6 +7560,8 @@
       <c r="O228" s="1"/>
       <c r="P228" s="1"/>
       <c r="Q228" s="1"/>
+      <c r="R228" s="1"/>
+      <c r="S228" s="1"/>
     </row>
     <row r="229">
       <c r="A229" s="1"/>
@@ -6878,6 +7581,8 @@
       <c r="O229" s="1"/>
       <c r="P229" s="1"/>
       <c r="Q229" s="1"/>
+      <c r="R229" s="1"/>
+      <c r="S229" s="1"/>
     </row>
     <row r="230">
       <c r="A230" s="1"/>
@@ -6897,6 +7602,8 @@
       <c r="O230" s="1"/>
       <c r="P230" s="1"/>
       <c r="Q230" s="1"/>
+      <c r="R230" s="1"/>
+      <c r="S230" s="1"/>
     </row>
     <row r="231">
       <c r="A231" s="1"/>
@@ -6916,6 +7623,8 @@
       <c r="O231" s="1"/>
       <c r="P231" s="1"/>
       <c r="Q231" s="1"/>
+      <c r="R231" s="1"/>
+      <c r="S231" s="1"/>
     </row>
     <row r="232">
       <c r="A232" s="1"/>
@@ -6935,6 +7644,8 @@
       <c r="O232" s="1"/>
       <c r="P232" s="1"/>
       <c r="Q232" s="1"/>
+      <c r="R232" s="1"/>
+      <c r="S232" s="1"/>
     </row>
     <row r="233">
       <c r="A233" s="1"/>
@@ -6954,6 +7665,8 @@
       <c r="O233" s="1"/>
       <c r="P233" s="1"/>
       <c r="Q233" s="1"/>
+      <c r="R233" s="1"/>
+      <c r="S233" s="1"/>
     </row>
     <row r="234">
       <c r="A234" s="1"/>
@@ -6973,6 +7686,8 @@
       <c r="O234" s="1"/>
       <c r="P234" s="1"/>
       <c r="Q234" s="1"/>
+      <c r="R234" s="1"/>
+      <c r="S234" s="1"/>
     </row>
     <row r="235">
       <c r="A235" s="1"/>
@@ -6992,6 +7707,8 @@
       <c r="O235" s="1"/>
       <c r="P235" s="1"/>
       <c r="Q235" s="1"/>
+      <c r="R235" s="1"/>
+      <c r="S235" s="1"/>
     </row>
     <row r="236">
       <c r="A236" s="1"/>
@@ -7011,6 +7728,8 @@
       <c r="O236" s="1"/>
       <c r="P236" s="1"/>
       <c r="Q236" s="1"/>
+      <c r="R236" s="1"/>
+      <c r="S236" s="1"/>
     </row>
     <row r="237">
       <c r="A237" s="1"/>
@@ -7030,6 +7749,8 @@
       <c r="O237" s="1"/>
       <c r="P237" s="1"/>
       <c r="Q237" s="1"/>
+      <c r="R237" s="1"/>
+      <c r="S237" s="1"/>
     </row>
     <row r="238">
       <c r="A238" s="1"/>
@@ -7049,6 +7770,8 @@
       <c r="O238" s="1"/>
       <c r="P238" s="1"/>
       <c r="Q238" s="1"/>
+      <c r="R238" s="1"/>
+      <c r="S238" s="1"/>
     </row>
     <row r="239">
       <c r="A239" s="1"/>
@@ -7068,6 +7791,8 @@
       <c r="O239" s="1"/>
       <c r="P239" s="1"/>
       <c r="Q239" s="1"/>
+      <c r="R239" s="1"/>
+      <c r="S239" s="1"/>
     </row>
     <row r="240">
       <c r="A240" s="1"/>
@@ -7087,6 +7812,8 @@
       <c r="O240" s="1"/>
       <c r="P240" s="1"/>
       <c r="Q240" s="1"/>
+      <c r="R240" s="1"/>
+      <c r="S240" s="1"/>
     </row>
     <row r="241">
       <c r="A241" s="1"/>
@@ -7106,6 +7833,8 @@
       <c r="O241" s="1"/>
       <c r="P241" s="1"/>
       <c r="Q241" s="1"/>
+      <c r="R241" s="1"/>
+      <c r="S241" s="1"/>
     </row>
     <row r="242">
       <c r="A242" s="1"/>
@@ -7125,6 +7854,8 @@
       <c r="O242" s="1"/>
       <c r="P242" s="1"/>
       <c r="Q242" s="1"/>
+      <c r="R242" s="1"/>
+      <c r="S242" s="1"/>
     </row>
     <row r="243">
       <c r="A243" s="1"/>
@@ -7144,6 +7875,8 @@
       <c r="O243" s="1"/>
       <c r="P243" s="1"/>
       <c r="Q243" s="1"/>
+      <c r="R243" s="1"/>
+      <c r="S243" s="1"/>
     </row>
     <row r="244">
       <c r="A244" s="1"/>
@@ -7163,6 +7896,8 @@
       <c r="O244" s="1"/>
       <c r="P244" s="1"/>
       <c r="Q244" s="1"/>
+      <c r="R244" s="1"/>
+      <c r="S244" s="1"/>
     </row>
     <row r="245">
       <c r="A245" s="1"/>
@@ -7182,6 +7917,8 @@
       <c r="O245" s="1"/>
       <c r="P245" s="1"/>
       <c r="Q245" s="1"/>
+      <c r="R245" s="1"/>
+      <c r="S245" s="1"/>
     </row>
     <row r="246">
       <c r="A246" s="1"/>
@@ -7201,6 +7938,8 @@
       <c r="O246" s="1"/>
       <c r="P246" s="1"/>
       <c r="Q246" s="1"/>
+      <c r="R246" s="1"/>
+      <c r="S246" s="1"/>
     </row>
     <row r="247">
       <c r="A247" s="1"/>
@@ -7220,6 +7959,8 @@
       <c r="O247" s="1"/>
       <c r="P247" s="1"/>
       <c r="Q247" s="1"/>
+      <c r="R247" s="1"/>
+      <c r="S247" s="1"/>
     </row>
     <row r="248">
       <c r="A248" s="1"/>
@@ -7239,6 +7980,8 @@
       <c r="O248" s="1"/>
       <c r="P248" s="1"/>
       <c r="Q248" s="1"/>
+      <c r="R248" s="1"/>
+      <c r="S248" s="1"/>
     </row>
     <row r="249">
       <c r="A249" s="1"/>
@@ -7258,6 +8001,8 @@
       <c r="O249" s="1"/>
       <c r="P249" s="1"/>
       <c r="Q249" s="1"/>
+      <c r="R249" s="1"/>
+      <c r="S249" s="1"/>
     </row>
     <row r="250">
       <c r="A250" s="1"/>
@@ -7277,6 +8022,8 @@
       <c r="O250" s="1"/>
       <c r="P250" s="1"/>
       <c r="Q250" s="1"/>
+      <c r="R250" s="1"/>
+      <c r="S250" s="1"/>
     </row>
     <row r="251">
       <c r="A251" s="1"/>
@@ -7296,6 +8043,8 @@
       <c r="O251" s="1"/>
       <c r="P251" s="1"/>
       <c r="Q251" s="1"/>
+      <c r="R251" s="1"/>
+      <c r="S251" s="1"/>
     </row>
     <row r="252">
       <c r="A252" s="1"/>
@@ -7315,6 +8064,8 @@
       <c r="O252" s="1"/>
       <c r="P252" s="1"/>
       <c r="Q252" s="1"/>
+      <c r="R252" s="1"/>
+      <c r="S252" s="1"/>
     </row>
     <row r="253">
       <c r="A253" s="1"/>
@@ -7334,6 +8085,8 @@
       <c r="O253" s="1"/>
       <c r="P253" s="1"/>
       <c r="Q253" s="1"/>
+      <c r="R253" s="1"/>
+      <c r="S253" s="1"/>
     </row>
     <row r="254">
       <c r="A254" s="1"/>
@@ -7353,6 +8106,8 @@
       <c r="O254" s="1"/>
       <c r="P254" s="1"/>
       <c r="Q254" s="1"/>
+      <c r="R254" s="1"/>
+      <c r="S254" s="1"/>
     </row>
     <row r="255">
       <c r="A255" s="1"/>
@@ -7372,6 +8127,8 @@
       <c r="O255" s="1"/>
       <c r="P255" s="1"/>
       <c r="Q255" s="1"/>
+      <c r="R255" s="1"/>
+      <c r="S255" s="1"/>
     </row>
     <row r="256">
       <c r="A256" s="1"/>
@@ -7391,6 +8148,8 @@
       <c r="O256" s="1"/>
       <c r="P256" s="1"/>
       <c r="Q256" s="1"/>
+      <c r="R256" s="1"/>
+      <c r="S256" s="1"/>
     </row>
     <row r="257">
       <c r="A257" s="1"/>
@@ -7410,6 +8169,8 @@
       <c r="O257" s="1"/>
       <c r="P257" s="1"/>
       <c r="Q257" s="1"/>
+      <c r="R257" s="1"/>
+      <c r="S257" s="1"/>
     </row>
     <row r="258">
       <c r="A258" s="1"/>
@@ -7429,6 +8190,8 @@
       <c r="O258" s="1"/>
       <c r="P258" s="1"/>
       <c r="Q258" s="1"/>
+      <c r="R258" s="1"/>
+      <c r="S258" s="1"/>
     </row>
     <row r="259">
       <c r="A259" s="1"/>
@@ -7448,9 +8211,11 @@
       <c r="O259" s="1"/>
       <c r="P259" s="1"/>
       <c r="Q259" s="1"/>
+      <c r="R259" s="1"/>
+      <c r="S259" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q59"/>
+  <autoFilter ref="A1:S59"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/data/raw/Democracy in Action/review/dia_2012_newspapers_review.xlsx
+++ b/data/raw/Democracy in Action/review/dia_2012_newspapers_review.xlsx
@@ -1,892 +1,953 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/katherineparslow/Documents/repos/presidential-endorsements/data/raw/Democracy in Action/review/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9D9BDD-C729-BC41-A5BD-BAA91F3F4B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="review" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="review" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review'!$A$1:$S$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">review!$A$1:$S$59</definedName>
   </definedNames>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="287">
-  <si>
-    <t xml:space="preserve">row_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">review_action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">review_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contest_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">party</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endorsee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endorser_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endorser_description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endorser_party_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">district</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_raw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">switch_direction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">switch_candidate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evidence_url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parsed_ok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raw_text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">2012R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newspaper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FALSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[UNMATCHED] National Review - not Gingrich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ron Paul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Daily Iowan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec. 12, 2011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">the University of Iowa student newspaper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dailyiowan121211.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Daily Iowan ...the University of Iowa student newspaper (Dec. 12, 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitt Romney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quad-City Times</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan. 1, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qctimes010112.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quad-City Times (Jan. 1, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterloo Cedar Falls Courier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">more of a push than an official endorsement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wcfcourier010112.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterloo Cedar Falls Courier (Jan. 1, 2012...more of a push than an official endorsement)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iowa City Press-Citizen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec. 28, 2011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">presscitizen122811.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iowa City Press-Citizen (Dec. 28, 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Des Moines Register</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec. 18, 2011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dmr121811.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Des Moines Register (Dec. 18, 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sioux City Journal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec. 4, 2011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scjournal120411.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sioux City Journal (Dec. 4, 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newt Gingrich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Hampshire Union Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nov. 27, 2011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.p2012.org/media/newspendorse/unionleader112711.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Hampshire Union Leader (Nov. 27, 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jon Huntsman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laconia Citizen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan. 6, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">citizen010612.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laconia Citizen (Jan. 6, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston Globe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston Globe [MA] (Jan. 6, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eagle Times</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan. 5, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claremont</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eagletimes010512.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eagle Times [Claremont] (Jan. 5, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The New Hampshire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNH student newspaper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tnh010512.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The New Hampshire ...UNH student newspaper (Jan. 5, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monadnock Ledger-Transcript</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monadnocklt122811.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monadnock Ledger-Transcript (Dec. 28, 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concord Monitor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec. 22, 2011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">concordmonitor122211.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concord Monitor (Dec. 22, 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keene Sentinel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">keenesentinel121811.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keene Sentinel (Dec. 18, 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Valley News</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valleynews121811.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Valley News (Dec. 18, 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eagle-Tribune</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North Andover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eagletribune010612.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eagle-Tribune [North Andover, MA] (Jan. 6, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nashua Telegraph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nashuatelegraph010512.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nashua Telegraph (Jan. 5, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Weirs Times</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec. 29, 2011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weirstimes122911.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Weirs Times (Dec. 29, 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston Herald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bostonherald122811.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston Herald [MA] (Dec. 28, 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conway Daily Sun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conway Daily Sun (Dec. 22, 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seacoast Media Group - Portsmouth Herald, Hampton Union and Exeter News-Letter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seacoast Media Group - Portsmouth Herald, Hampton Union and Exeter News-Letter (Dec. 18, 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foster's Daily Democrat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fosters120411.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foster's Daily Democrat (Dec. 4, 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The State</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan. 15, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columbia; out Jan. 16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">thestate011512.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The State [Columbia] (Jan. 15, 2012)...out Jan. 16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Post and Courier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan. 20, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">postandcourier012012.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Post and Courier (Jan. 20, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Herald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan. 19, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rock Hill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Herald [Rock Hill] (Jan. 19, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columbia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">thestate011912.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The State [Columbia] (Jan. 19, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spartanburg Herald-Journal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan. 17, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spartanburg Herald-Journal (Jan. 17, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greenville News</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greenville News (Jan. 15, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlotte Observer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">charlotteobserver011512.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charlotte Observer [NC] (Jan. 15, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tampa Tribune</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan. 29, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www2.tbo.com/news/opinion/2012/jan/29/vwopino1-gingrich-in-gop-primary-ar-352239/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tampa Tribune (Jan. 29, 2012) +</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orlando Sentinel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan. 25, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.orlandosentinel.com/news/opinion/os-ed-gop-primary-endorsement-012512-20120124,0,7675538.story</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orlando Sentinel (Jan. 25, 2012) +</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pensacola News Journal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan. 22, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.pnj.com/article/20120122/OPINION/201220308/For-GOP-nomination-Mitt-Romney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pensacola News Journal (Jan. 22, 2012) +</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tampa Bay Times</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.tampabay.com/opinion/editorials/article1210848.ece</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tampa Bay Times (Jan. 17, 2012) +</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Independent Florida Alligator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University of Florida student newspaper; Gainesville</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.alligator.org/opinion/editorials/article_ffe61da4-470a-11e1-b4f0-0019bb2963f4.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Independent Florida Alligator ...University of Florida (Gainesville) student newspaper (Jan. 25, 2012) +</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reno Gazette-Journal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb. 3, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rgj020312.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reno Gazette-Journal (Feb. 3, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Vegas Review-Journal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lvrj012912.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Vegas Review-Journal (Jan. 29, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denver Post</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denver Post (Feb. 3, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arizona Republic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb. 24, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.azcentral.com/arizonarepublic/opinions/articles/2012/02/23/20120223editoriarl0224-romney-right-these-times.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arizona Republic (Feb. 24, 2012) +</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Midland Daily News</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb. 26, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.ourmidland.com/opinion/article_7ff8e090-609b-11e1-b91e-001871e3ce6c.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Midland Daily News (Feb. 26, 2012) +</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detroit Free Press</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb. 23, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.freep.com/article/20120223/OPINION01/120222077/Free-Press-endorsement-Mitt-Romney-is-best-but-we-urge-him-to-recapture-collaborative-spirit-GOP-primary-Michigan-Republican</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detroit Free Press (Feb. 23, 2012) +</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grand Rapids Press</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb. 22, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.mlive.com/opinion/grand-rapids/index.ssf/2012/02/grand_rapids_editorial_mitt_ro.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grand Rapids Press (Feb. 22, 2012) +</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detroit News</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.detroitnews.com/article/20120222/OPINION01/202220315/1022/politics/Detroit-News-endorsement-Mitt-Romney-Michigan-GOP-primary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detroit News (Feb. 22, 2012) +</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oakland Press</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb. 21, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.theoaklandpress.com/articles/2012/02/21/opinion/doc4f43d95e993d2684728787.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oakland Press (Feb. 21, 2012) +</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arab American News</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arabamericannews022412.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arab American News (Feb. 24, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Albany Herald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">March 3, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Albany Herald (March 3, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savannah Morning News</t>
-  </si>
-  <si>
-    <t xml:space="preserve">March 1, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savannah Morning News (March 1, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Philadelphia Times-Reporter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">March 4, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Philadelphia Times-Reporter (March 4, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cincinnati Enquirer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cincinnati Enquirer (March 3, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cleveland Plain-Dealer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cleveland Plain-Dealer (March 3, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columbus Dispatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb. 5, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columbus Dispatch (Feb. 5, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Oklahoman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Oklahoman (Dec. 18, 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Times Daily</t>
-  </si>
-  <si>
-    <t xml:space="preserve">March 9, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Times Daily (Florence) (March 9, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Birmingham News</t>
-  </si>
-  <si>
-    <t xml:space="preserve">March 7, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Birmingham News (March 7, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peoria Journal Star</t>
-  </si>
-  <si>
-    <t xml:space="preserve">March 18, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peoria Journal Star (March 18, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chicago Tribune</t>
-  </si>
-  <si>
-    <t xml:space="preserve">March 17, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">online March 16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chicago Tribune (March 17, 2012; online March 16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Herald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arlington Heights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Herald [Arlington Heights] (March 4, 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milwaukee Journal Sentinel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">April 1, 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">online March 31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.jsonline.com/news/opinion/romneys-pragmatism-makes-him-the-best-pick-e24q8uu-145232155.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milwaukee Journal Sentinel (April 1, 2012; online March 31) +</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="306">
+  <si>
+    <t>row_id</t>
+  </si>
+  <si>
+    <t>review_action</t>
+  </si>
+  <si>
+    <t>review_note</t>
+  </si>
+  <si>
+    <t>contest_id</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>party</t>
+  </si>
+  <si>
+    <t>endorsee</t>
+  </si>
+  <si>
+    <t>endorser_name</t>
+  </si>
+  <si>
+    <t>endorser_description</t>
+  </si>
+  <si>
+    <t>endorser_party_note</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>district</t>
+  </si>
+  <si>
+    <t>date_raw</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>switch_direction</t>
+  </si>
+  <si>
+    <t>switch_candidate</t>
+  </si>
+  <si>
+    <t>evidence_url</t>
+  </si>
+  <si>
+    <t>parsed_ok</t>
+  </si>
+  <si>
+    <t>raw_text</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2012R</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Newspaper</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>[UNMATCHED] National Review - not Gingrich</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Ron Paul</t>
+  </si>
+  <si>
+    <t>The Daily Iowan</t>
+  </si>
+  <si>
+    <t>Dec. 12, 2011</t>
+  </si>
+  <si>
+    <t>the University of Iowa student newspaper</t>
+  </si>
+  <si>
+    <t>dailyiowan121211.html</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>The Daily Iowan ...the University of Iowa student newspaper (Dec. 12, 2011)</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Mitt Romney</t>
+  </si>
+  <si>
+    <t>Quad-City Times</t>
+  </si>
+  <si>
+    <t>Jan. 1, 2012</t>
+  </si>
+  <si>
+    <t>qctimes010112.html</t>
+  </si>
+  <si>
+    <t>Quad-City Times (Jan. 1, 2012)</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Waterloo Cedar Falls Courier</t>
+  </si>
+  <si>
+    <t>more of a push than an official endorsement</t>
+  </si>
+  <si>
+    <t>wcfcourier010112.html</t>
+  </si>
+  <si>
+    <t>Waterloo Cedar Falls Courier (Jan. 1, 2012...more of a push than an official endorsement)</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Iowa City Press-Citizen</t>
+  </si>
+  <si>
+    <t>Dec. 28, 2011</t>
+  </si>
+  <si>
+    <t>presscitizen122811.html</t>
+  </si>
+  <si>
+    <t>Iowa City Press-Citizen (Dec. 28, 2011)</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Des Moines Register</t>
+  </si>
+  <si>
+    <t>Dec. 18, 2011</t>
+  </si>
+  <si>
+    <t>dmr121811.html</t>
+  </si>
+  <si>
+    <t>Des Moines Register (Dec. 18, 2011)</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Sioux City Journal</t>
+  </si>
+  <si>
+    <t>Dec. 4, 2011</t>
+  </si>
+  <si>
+    <t>scjournal120411.html</t>
+  </si>
+  <si>
+    <t>Sioux City Journal (Dec. 4, 2011)</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Newt Gingrich</t>
+  </si>
+  <si>
+    <t>New Hampshire Union Leader</t>
+  </si>
+  <si>
+    <t>Nov. 27, 2011</t>
+  </si>
+  <si>
+    <t>https://www.p2012.org/media/newspendorse/unionleader112711.html</t>
+  </si>
+  <si>
+    <t>New Hampshire Union Leader (Nov. 27, 2011)</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Jon Huntsman</t>
+  </si>
+  <si>
+    <t>Laconia Citizen</t>
+  </si>
+  <si>
+    <t>Jan. 6, 2012</t>
+  </si>
+  <si>
+    <t>citizen010612.html</t>
+  </si>
+  <si>
+    <t>Laconia Citizen (Jan. 6, 2012)</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Boston Globe</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>Boston Globe [MA] (Jan. 6, 2012)</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Eagle Times</t>
+  </si>
+  <si>
+    <t>Jan. 5, 2012</t>
+  </si>
+  <si>
+    <t>Claremont</t>
+  </si>
+  <si>
+    <t>eagletimes010512.html</t>
+  </si>
+  <si>
+    <t>Eagle Times [Claremont] (Jan. 5, 2012)</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>The New Hampshire</t>
+  </si>
+  <si>
+    <t>UNH student newspaper</t>
+  </si>
+  <si>
+    <t>tnh010512.html</t>
+  </si>
+  <si>
+    <t>The New Hampshire ...UNH student newspaper (Jan. 5, 2012)</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Monadnock Ledger-Transcript</t>
+  </si>
+  <si>
+    <t>monadnocklt122811.html</t>
+  </si>
+  <si>
+    <t>Monadnock Ledger-Transcript (Dec. 28, 2011)</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Concord Monitor</t>
+  </si>
+  <si>
+    <t>Dec. 22, 2011</t>
+  </si>
+  <si>
+    <t>concordmonitor122211.html</t>
+  </si>
+  <si>
+    <t>Concord Monitor (Dec. 22, 2011)</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Keene Sentinel</t>
+  </si>
+  <si>
+    <t>keenesentinel121811.html</t>
+  </si>
+  <si>
+    <t>Keene Sentinel (Dec. 18, 2011)</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>The Valley News</t>
+  </si>
+  <si>
+    <t>valleynews121811.html</t>
+  </si>
+  <si>
+    <t>The Valley News (Dec. 18, 2011)</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Eagle-Tribune</t>
+  </si>
+  <si>
+    <t>North Andover</t>
+  </si>
+  <si>
+    <t>eagletribune010612.html</t>
+  </si>
+  <si>
+    <t>Eagle-Tribune [North Andover, MA] (Jan. 6, 2012)</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Nashua Telegraph</t>
+  </si>
+  <si>
+    <t>nashuatelegraph010512.html</t>
+  </si>
+  <si>
+    <t>Nashua Telegraph (Jan. 5, 2012)</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>The Weirs Times</t>
+  </si>
+  <si>
+    <t>Dec. 29, 2011</t>
+  </si>
+  <si>
+    <t>weirstimes122911.html</t>
+  </si>
+  <si>
+    <t>The Weirs Times (Dec. 29, 2011)</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Boston Herald</t>
+  </si>
+  <si>
+    <t>bostonherald122811.html</t>
+  </si>
+  <si>
+    <t>Boston Herald [MA] (Dec. 28, 2011)</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Conway Daily Sun</t>
+  </si>
+  <si>
+    <t>Conway Daily Sun (Dec. 22, 2011)</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Seacoast Media Group - Portsmouth Herald, Hampton Union and Exeter News-Letter</t>
+  </si>
+  <si>
+    <t>Seacoast Media Group - Portsmouth Herald, Hampton Union and Exeter News-Letter (Dec. 18, 2011)</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Foster's Daily Democrat</t>
+  </si>
+  <si>
+    <t>fosters120411.html</t>
+  </si>
+  <si>
+    <t>Foster's Daily Democrat (Dec. 4, 2011)</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>The State</t>
+  </si>
+  <si>
+    <t>Jan. 15, 2012</t>
+  </si>
+  <si>
+    <t>Columbia; out Jan. 16</t>
+  </si>
+  <si>
+    <t>thestate011512.html</t>
+  </si>
+  <si>
+    <t>The State [Columbia] (Jan. 15, 2012)...out Jan. 16</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>The Post and Courier</t>
+  </si>
+  <si>
+    <t>Jan. 20, 2012</t>
+  </si>
+  <si>
+    <t>postandcourier012012.html</t>
+  </si>
+  <si>
+    <t>The Post and Courier (Jan. 20, 2012)</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>The Herald</t>
+  </si>
+  <si>
+    <t>Jan. 19, 2012</t>
+  </si>
+  <si>
+    <t>Rock Hill</t>
+  </si>
+  <si>
+    <t>The Herald [Rock Hill] (Jan. 19, 2012)</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Columbia</t>
+  </si>
+  <si>
+    <t>thestate011912.html</t>
+  </si>
+  <si>
+    <t>The State [Columbia] (Jan. 19, 2012)</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Spartanburg Herald-Journal</t>
+  </si>
+  <si>
+    <t>Jan. 17, 2012</t>
+  </si>
+  <si>
+    <t>Spartanburg Herald-Journal (Jan. 17, 2012)</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Greenville News</t>
+  </si>
+  <si>
+    <t>Greenville News (Jan. 15, 2012)</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Charlotte Observer</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>charlotteobserver011512.html</t>
+  </si>
+  <si>
+    <t>Charlotte Observer [NC] (Jan. 15, 2012)</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Tampa Tribune</t>
+  </si>
+  <si>
+    <t>Jan. 29, 2012</t>
+  </si>
+  <si>
+    <t>http://www2.tbo.com/news/opinion/2012/jan/29/vwopino1-gingrich-in-gop-primary-ar-352239/</t>
+  </si>
+  <si>
+    <t>Tampa Tribune (Jan. 29, 2012) +</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Orlando Sentinel</t>
+  </si>
+  <si>
+    <t>Jan. 25, 2012</t>
+  </si>
+  <si>
+    <t>http://www.orlandosentinel.com/news/opinion/os-ed-gop-primary-endorsement-012512-20120124,0,7675538.story</t>
+  </si>
+  <si>
+    <t>Orlando Sentinel (Jan. 25, 2012) +</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Pensacola News Journal</t>
+  </si>
+  <si>
+    <t>Jan. 22, 2012</t>
+  </si>
+  <si>
+    <t>http://www.pnj.com/article/20120122/OPINION/201220308/For-GOP-nomination-Mitt-Romney</t>
+  </si>
+  <si>
+    <t>Pensacola News Journal (Jan. 22, 2012) +</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Tampa Bay Times</t>
+  </si>
+  <si>
+    <t>http://www.tampabay.com/opinion/editorials/article1210848.ece</t>
+  </si>
+  <si>
+    <t>Tampa Bay Times (Jan. 17, 2012) +</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>The Independent Florida Alligator</t>
+  </si>
+  <si>
+    <t>University of Florida student newspaper; Gainesville</t>
+  </si>
+  <si>
+    <t>http://www.alligator.org/opinion/editorials/article_ffe61da4-470a-11e1-b4f0-0019bb2963f4.html</t>
+  </si>
+  <si>
+    <t>The Independent Florida Alligator ...University of Florida (Gainesville) student newspaper (Jan. 25, 2012) +</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Reno Gazette-Journal</t>
+  </si>
+  <si>
+    <t>Feb. 3, 2012</t>
+  </si>
+  <si>
+    <t>rgj020312.html</t>
+  </si>
+  <si>
+    <t>Reno Gazette-Journal (Feb. 3, 2012)</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Las Vegas Review-Journal</t>
+  </si>
+  <si>
+    <t>lvrj012912.html</t>
+  </si>
+  <si>
+    <t>Las Vegas Review-Journal (Jan. 29, 2012)</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Denver Post</t>
+  </si>
+  <si>
+    <t>Denver Post (Feb. 3, 2012)</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Arizona Republic</t>
+  </si>
+  <si>
+    <t>Feb. 24, 2012</t>
+  </si>
+  <si>
+    <t>http://www.azcentral.com/arizonarepublic/opinions/articles/2012/02/23/20120223editoriarl0224-romney-right-these-times.html</t>
+  </si>
+  <si>
+    <t>Arizona Republic (Feb. 24, 2012) +</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Midland Daily News</t>
+  </si>
+  <si>
+    <t>Feb. 26, 2012</t>
+  </si>
+  <si>
+    <t>http://www.ourmidland.com/opinion/article_7ff8e090-609b-11e1-b91e-001871e3ce6c.html</t>
+  </si>
+  <si>
+    <t>Midland Daily News (Feb. 26, 2012) +</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Detroit Free Press</t>
+  </si>
+  <si>
+    <t>Feb. 23, 2012</t>
+  </si>
+  <si>
+    <t>http://www.freep.com/article/20120223/OPINION01/120222077/Free-Press-endorsement-Mitt-Romney-is-best-but-we-urge-him-to-recapture-collaborative-spirit-GOP-primary-Michigan-Republican</t>
+  </si>
+  <si>
+    <t>Detroit Free Press (Feb. 23, 2012) +</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Grand Rapids Press</t>
+  </si>
+  <si>
+    <t>Feb. 22, 2012</t>
+  </si>
+  <si>
+    <t>http://www.mlive.com/opinion/grand-rapids/index.ssf/2012/02/grand_rapids_editorial_mitt_ro.html</t>
+  </si>
+  <si>
+    <t>Grand Rapids Press (Feb. 22, 2012) +</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Detroit News</t>
+  </si>
+  <si>
+    <t>http://www.detroitnews.com/article/20120222/OPINION01/202220315/1022/politics/Detroit-News-endorsement-Mitt-Romney-Michigan-GOP-primary</t>
+  </si>
+  <si>
+    <t>Detroit News (Feb. 22, 2012) +</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Oakland Press</t>
+  </si>
+  <si>
+    <t>Feb. 21, 2012</t>
+  </si>
+  <si>
+    <t>http://www.theoaklandpress.com/articles/2012/02/21/opinion/doc4f43d95e993d2684728787.txt</t>
+  </si>
+  <si>
+    <t>Oakland Press (Feb. 21, 2012) +</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Arab American News</t>
+  </si>
+  <si>
+    <t>arabamericannews022412.html</t>
+  </si>
+  <si>
+    <t>Arab American News (Feb. 24, 2012)</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Albany Herald</t>
+  </si>
+  <si>
+    <t>March 3, 2012</t>
+  </si>
+  <si>
+    <t>Albany Herald (March 3, 2012)</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>Savannah Morning News</t>
+  </si>
+  <si>
+    <t>March 1, 2012</t>
+  </si>
+  <si>
+    <t>Savannah Morning News (March 1, 2012)</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>New Philadelphia Times-Reporter</t>
+  </si>
+  <si>
+    <t>March 4, 2012</t>
+  </si>
+  <si>
+    <t>New Philadelphia Times-Reporter (March 4, 2012)</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Cincinnati Enquirer</t>
+  </si>
+  <si>
+    <t>Cincinnati Enquirer (March 3, 2012)</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Cleveland Plain-Dealer</t>
+  </si>
+  <si>
+    <t>Cleveland Plain-Dealer (March 3, 2012)</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>Columbus Dispatch</t>
+  </si>
+  <si>
+    <t>Feb. 5, 2012</t>
+  </si>
+  <si>
+    <t>Columbus Dispatch (Feb. 5, 2012)</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>The Oklahoman</t>
+  </si>
+  <si>
+    <t>The Oklahoman (Dec. 18, 2011)</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>Times Daily</t>
+  </si>
+  <si>
+    <t>March 9, 2012</t>
+  </si>
+  <si>
+    <t>Florence</t>
+  </si>
+  <si>
+    <t>Times Daily (Florence) (March 9, 2012)</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Birmingham News</t>
+  </si>
+  <si>
+    <t>March 7, 2012</t>
+  </si>
+  <si>
+    <t>Birmingham News (March 7, 2012)</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Peoria Journal Star</t>
+  </si>
+  <si>
+    <t>March 18, 2012</t>
+  </si>
+  <si>
+    <t>Peoria Journal Star (March 18, 2012)</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>Chicago Tribune</t>
+  </si>
+  <si>
+    <t>March 17, 2012</t>
+  </si>
+  <si>
+    <t>online March 16</t>
+  </si>
+  <si>
+    <t>Chicago Tribune (March 17, 2012; online March 16)</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>Daily Herald</t>
+  </si>
+  <si>
+    <t>Arlington Heights</t>
+  </si>
+  <si>
+    <t>Daily Herald [Arlington Heights] (March 4, 2012)</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>Milwaukee Journal Sentinel</t>
+  </si>
+  <si>
+    <t>April 1, 2012</t>
+  </si>
+  <si>
+    <t>online March 31</t>
+  </si>
+  <si>
+    <t>http://www.jsonline.com/news/opinion/romneys-pragmatism-makes-him-the-best-pick-e24q8uu-145232155.html</t>
+  </si>
+  <si>
+    <t>Milwaukee Journal Sentinel (April 1, 2012; online March 31) +</t>
+  </si>
+  <si>
+    <t>drop</t>
+  </si>
+  <si>
+    <t>endorsement against Gingrich, not for any candidate</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>edited</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>NV</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>OH</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>state from page section heading</t>
+  </si>
+  <si>
+    <t>state from page section heading; one entry for three papers in the same group; likely one shared editorial</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="@"/>
-    <numFmt numFmtId="166" formatCode="@"/>
-  </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -898,12 +959,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <b/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -928,13 +991,22 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1216,32 +1288,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S259"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="40.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="8.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="8.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="40.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="22.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="21.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="8.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="10.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="16.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="40.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="18.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="40.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="11.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="80.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="40.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="6" width="8.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" customWidth="1"/>
+    <col min="8" max="8" width="40.6640625" customWidth="1"/>
+    <col min="9" max="9" width="22.6640625" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="40.6640625" customWidth="1"/>
+    <col min="15" max="16" width="18.6640625" customWidth="1"/>
+    <col min="17" max="17" width="40.6640625" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" customWidth="1"/>
+    <col min="19" max="19" width="80.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1300,15 +1370,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>21</v>
@@ -1339,15 +1409,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C3" t="s">
+        <v>304</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>21</v>
@@ -1368,7 +1438,9 @@
         <v>24</v>
       </c>
       <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
+      <c r="K3" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1" t="s">
         <v>30</v>
@@ -1388,15 +1460,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C4" t="s">
+        <v>304</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>21</v>
@@ -1417,7 +1489,9 @@
         <v>24</v>
       </c>
       <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+      <c r="K4" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
         <v>38</v>
@@ -1435,15 +1509,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C5" t="s">
+        <v>304</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>21</v>
@@ -1464,7 +1538,9 @@
         <v>24</v>
       </c>
       <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
         <v>38</v>
@@ -1484,15 +1560,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C6" t="s">
+        <v>304</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>21</v>
@@ -1513,7 +1589,9 @@
         <v>24</v>
       </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
         <v>48</v>
@@ -1531,15 +1609,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C7" t="s">
+        <v>304</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>21</v>
@@ -1560,7 +1638,9 @@
         <v>24</v>
       </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
         <v>53</v>
@@ -1578,15 +1658,15 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C8" t="s">
+        <v>304</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>21</v>
@@ -1607,7 +1687,9 @@
         <v>24</v>
       </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
         <v>58</v>
@@ -1625,15 +1707,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C9" t="s">
+        <v>304</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>21</v>
@@ -1654,7 +1736,9 @@
         <v>24</v>
       </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1" t="s">
         <v>64</v>
@@ -1672,15 +1756,15 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C10" t="s">
+        <v>304</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>21</v>
@@ -1701,7 +1785,9 @@
         <v>24</v>
       </c>
       <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
+      <c r="K10" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
         <v>70</v>
@@ -1719,7 +1805,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>73</v>
       </c>
@@ -1766,15 +1852,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C12" t="s">
+        <v>304</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>21</v>
@@ -1795,7 +1881,9 @@
         <v>24</v>
       </c>
       <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
+      <c r="K12" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
         <v>79</v>
@@ -1815,15 +1903,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C13" t="s">
+        <v>304</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>21</v>
@@ -1844,7 +1932,9 @@
         <v>24</v>
       </c>
       <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+      <c r="K13" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1" t="s">
         <v>79</v>
@@ -1864,15 +1954,15 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>88</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C14" t="s">
+        <v>304</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>21</v>
@@ -1893,7 +1983,9 @@
         <v>24</v>
       </c>
       <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
+      <c r="K14" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1" t="s">
         <v>48</v>
@@ -1911,15 +2003,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C15" t="s">
+        <v>304</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>21</v>
@@ -1940,7 +2032,9 @@
         <v>24</v>
       </c>
       <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1" t="s">
         <v>94</v>
@@ -1958,15 +2052,15 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C16" t="s">
+        <v>304</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>21</v>
@@ -1987,7 +2081,9 @@
         <v>24</v>
       </c>
       <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
+      <c r="K16" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1" t="s">
         <v>53</v>
@@ -2005,15 +2101,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C17" t="s">
+        <v>304</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>21</v>
@@ -2034,7 +2130,9 @@
         <v>24</v>
       </c>
       <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="s">
         <v>53</v>
@@ -2052,7 +2150,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>105</v>
       </c>
@@ -2103,15 +2201,15 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>110</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C19" t="s">
+        <v>304</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>21</v>
@@ -2132,7 +2230,9 @@
         <v>24</v>
       </c>
       <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
         <v>79</v>
@@ -2150,15 +2250,15 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>114</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C20" t="s">
+        <v>304</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>21</v>
@@ -2179,7 +2279,9 @@
         <v>24</v>
       </c>
       <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
+      <c r="K20" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1" t="s">
         <v>116</v>
@@ -2197,7 +2299,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>119</v>
       </c>
@@ -2246,15 +2348,15 @@
         <v>122</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C22" t="s">
+        <v>304</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>21</v>
@@ -2275,7 +2377,9 @@
         <v>24</v>
       </c>
       <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
+      <c r="K22" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
         <v>94</v>
@@ -2291,15 +2395,15 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>126</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C23" t="s">
+        <v>305</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>21</v>
@@ -2320,7 +2424,9 @@
         <v>24</v>
       </c>
       <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
+      <c r="K23" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
         <v>53</v>
@@ -2336,15 +2442,15 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>129</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C24" t="s">
+        <v>304</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>21</v>
@@ -2365,7 +2471,9 @@
         <v>24</v>
       </c>
       <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
+      <c r="K24" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
         <v>58</v>
@@ -2383,15 +2491,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>133</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C25" t="s">
+        <v>304</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>21</v>
@@ -2412,7 +2520,9 @@
         <v>24</v>
       </c>
       <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
+      <c r="K25" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1" t="s">
         <v>135</v>
@@ -2432,15 +2542,15 @@
         <v>138</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C26" t="s">
+        <v>304</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>21</v>
@@ -2461,7 +2571,9 @@
         <v>24</v>
       </c>
       <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
+      <c r="K26" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1" t="s">
         <v>141</v>
@@ -2479,15 +2591,15 @@
         <v>143</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C27" t="s">
+        <v>304</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>21</v>
@@ -2508,7 +2620,9 @@
         <v>24</v>
       </c>
       <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
+      <c r="K27" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1" t="s">
         <v>146</v>
@@ -2526,15 +2640,15 @@
         <v>148</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>149</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C28" t="s">
+        <v>304</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>21</v>
@@ -2555,7 +2669,9 @@
         <v>24</v>
       </c>
       <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
+      <c r="K28" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1" t="s">
         <v>146</v>
@@ -2575,15 +2691,15 @@
         <v>152</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>153</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C29" t="s">
+        <v>304</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>21</v>
@@ -2604,7 +2720,9 @@
         <v>24</v>
       </c>
       <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
+      <c r="K29" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1" t="s">
         <v>155</v>
@@ -2620,15 +2738,15 @@
         <v>156</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>157</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C30" t="s">
+        <v>304</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>21</v>
@@ -2649,7 +2767,9 @@
         <v>24</v>
       </c>
       <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
+      <c r="K30" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1" t="s">
         <v>135</v>
@@ -2665,7 +2785,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>160</v>
       </c>
@@ -2714,15 +2834,15 @@
         <v>164</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>165</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C32" t="s">
+        <v>304</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>21</v>
@@ -2743,7 +2863,9 @@
         <v>24</v>
       </c>
       <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
+      <c r="K32" s="1" t="s">
+        <v>293</v>
+      </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1" t="s">
         <v>167</v>
@@ -2761,15 +2883,15 @@
         <v>169</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>170</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C33" t="s">
+        <v>304</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>21</v>
@@ -2790,7 +2912,9 @@
         <v>24</v>
       </c>
       <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
+      <c r="K33" s="1" t="s">
+        <v>293</v>
+      </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
         <v>172</v>
@@ -2808,15 +2932,15 @@
         <v>174</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C34" t="s">
+        <v>304</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>21</v>
@@ -2837,7 +2961,9 @@
         <v>24</v>
       </c>
       <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
+      <c r="K34" s="1" t="s">
+        <v>293</v>
+      </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1" t="s">
         <v>177</v>
@@ -2855,15 +2981,15 @@
         <v>179</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>180</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C35" t="s">
+        <v>304</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>21</v>
@@ -2884,7 +3010,9 @@
         <v>24</v>
       </c>
       <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
+      <c r="K35" s="1" t="s">
+        <v>293</v>
+      </c>
       <c r="L35" s="1"/>
       <c r="M35" s="1" t="s">
         <v>155</v>
@@ -2902,15 +3030,15 @@
         <v>183</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>184</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C36" t="s">
+        <v>304</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>21</v>
@@ -2931,7 +3059,9 @@
         <v>24</v>
       </c>
       <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
+      <c r="K36" s="1" t="s">
+        <v>293</v>
+      </c>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
         <v>172</v>
@@ -2951,15 +3081,15 @@
         <v>188</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>189</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C37" t="s">
+        <v>304</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>21</v>
@@ -2980,7 +3110,9 @@
         <v>24</v>
       </c>
       <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
+      <c r="K37" s="1" t="s">
+        <v>294</v>
+      </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
         <v>191</v>
@@ -2998,15 +3130,15 @@
         <v>193</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>194</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C38" t="s">
+        <v>304</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>21</v>
@@ -3027,7 +3159,9 @@
         <v>24</v>
       </c>
       <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
+      <c r="K38" s="1" t="s">
+        <v>294</v>
+      </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1" t="s">
         <v>167</v>
@@ -3045,15 +3179,15 @@
         <v>197</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>198</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C39" t="s">
+        <v>304</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>21</v>
@@ -3074,7 +3208,9 @@
         <v>24</v>
       </c>
       <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
+      <c r="K39" s="1" t="s">
+        <v>295</v>
+      </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1" t="s">
         <v>191</v>
@@ -3090,15 +3226,15 @@
         <v>200</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>201</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C40" t="s">
+        <v>304</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>21</v>
@@ -3119,7 +3255,9 @@
         <v>24</v>
       </c>
       <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
+      <c r="K40" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1" t="s">
         <v>203</v>
@@ -3137,15 +3275,15 @@
         <v>205</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>206</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C41" t="s">
+        <v>304</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>21</v>
@@ -3166,7 +3304,9 @@
         <v>24</v>
       </c>
       <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
+      <c r="K41" s="1" t="s">
+        <v>297</v>
+      </c>
       <c r="L41" s="1"/>
       <c r="M41" s="1" t="s">
         <v>208</v>
@@ -3184,15 +3324,15 @@
         <v>210</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>211</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C42" t="s">
+        <v>304</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>21</v>
@@ -3213,7 +3353,9 @@
         <v>24</v>
       </c>
       <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
+      <c r="K42" s="1" t="s">
+        <v>297</v>
+      </c>
       <c r="L42" s="1"/>
       <c r="M42" s="1" t="s">
         <v>213</v>
@@ -3231,15 +3373,15 @@
         <v>215</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>216</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C43" t="s">
+        <v>304</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>21</v>
@@ -3260,7 +3402,9 @@
         <v>24</v>
       </c>
       <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
+      <c r="K43" s="1" t="s">
+        <v>297</v>
+      </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1" t="s">
         <v>218</v>
@@ -3278,15 +3422,15 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>221</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C44" t="s">
+        <v>304</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>21</v>
@@ -3307,7 +3451,9 @@
         <v>24</v>
       </c>
       <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
+      <c r="K44" s="1" t="s">
+        <v>297</v>
+      </c>
       <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
         <v>218</v>
@@ -3325,15 +3471,15 @@
         <v>224</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>225</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C45" t="s">
+        <v>304</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>21</v>
@@ -3354,7 +3500,9 @@
         <v>24</v>
       </c>
       <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
+      <c r="K45" s="1" t="s">
+        <v>297</v>
+      </c>
       <c r="L45" s="1"/>
       <c r="M45" s="1" t="s">
         <v>227</v>
@@ -3372,15 +3520,15 @@
         <v>229</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>230</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C46" t="s">
+        <v>304</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>21</v>
@@ -3401,7 +3549,9 @@
         <v>24</v>
       </c>
       <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
+      <c r="K46" s="1" t="s">
+        <v>297</v>
+      </c>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="s">
         <v>203</v>
@@ -3419,15 +3569,15 @@
         <v>233</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>234</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C47" t="s">
+        <v>304</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>21</v>
@@ -3448,7 +3598,9 @@
         <v>24</v>
       </c>
       <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
+      <c r="K47" s="1" t="s">
+        <v>298</v>
+      </c>
       <c r="L47" s="1"/>
       <c r="M47" s="1" t="s">
         <v>236</v>
@@ -3464,15 +3616,15 @@
         <v>237</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>238</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C48" t="s">
+        <v>304</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>21</v>
@@ -3493,7 +3645,9 @@
         <v>24</v>
       </c>
       <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
+      <c r="K48" s="1" t="s">
+        <v>298</v>
+      </c>
       <c r="L48" s="1"/>
       <c r="M48" s="1" t="s">
         <v>240</v>
@@ -3509,15 +3663,15 @@
         <v>241</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>242</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C49" t="s">
+        <v>304</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>21</v>
@@ -3538,7 +3692,9 @@
         <v>24</v>
       </c>
       <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
+      <c r="K49" s="1" t="s">
+        <v>299</v>
+      </c>
       <c r="L49" s="1"/>
       <c r="M49" s="1" t="s">
         <v>244</v>
@@ -3554,15 +3710,15 @@
         <v>245</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>246</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C50" t="s">
+        <v>304</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>21</v>
@@ -3583,7 +3739,9 @@
         <v>24</v>
       </c>
       <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
+      <c r="K50" s="1" t="s">
+        <v>299</v>
+      </c>
       <c r="L50" s="1"/>
       <c r="M50" s="1" t="s">
         <v>236</v>
@@ -3599,15 +3757,15 @@
         <v>248</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>249</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C51" t="s">
+        <v>304</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>21</v>
@@ -3628,7 +3786,9 @@
         <v>24</v>
       </c>
       <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
+      <c r="K51" s="1" t="s">
+        <v>299</v>
+      </c>
       <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
         <v>236</v>
@@ -3644,15 +3804,15 @@
         <v>251</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>252</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C52" t="s">
+        <v>304</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>21</v>
@@ -3673,7 +3833,9 @@
         <v>24</v>
       </c>
       <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
+      <c r="K52" s="1" t="s">
+        <v>299</v>
+      </c>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="s">
         <v>254</v>
@@ -3689,15 +3851,15 @@
         <v>255</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>256</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C53" t="s">
+        <v>304</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>21</v>
@@ -3718,7 +3880,9 @@
         <v>24</v>
       </c>
       <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
+      <c r="K53" s="1" t="s">
+        <v>300</v>
+      </c>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
         <v>53</v>
@@ -3734,15 +3898,15 @@
         <v>258</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>259</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C54" t="s">
+        <v>304</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>21</v>
@@ -3763,7 +3927,9 @@
         <v>24</v>
       </c>
       <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
+      <c r="K54" s="1" t="s">
+        <v>301</v>
+      </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1" t="s">
         <v>261</v>
@@ -3781,15 +3947,15 @@
         <v>263</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>264</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C55" t="s">
+        <v>304</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>21</v>
@@ -3810,7 +3976,9 @@
         <v>24</v>
       </c>
       <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
+      <c r="K55" s="1" t="s">
+        <v>301</v>
+      </c>
       <c r="L55" s="1"/>
       <c r="M55" s="1" t="s">
         <v>266</v>
@@ -3826,15 +3994,15 @@
         <v>267</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>268</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C56" t="s">
+        <v>304</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>21</v>
@@ -3855,7 +4023,9 @@
         <v>24</v>
       </c>
       <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
+      <c r="K56" s="1" t="s">
+        <v>302</v>
+      </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="s">
         <v>270</v>
@@ -3871,15 +4041,15 @@
         <v>271</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>272</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C57" t="s">
+        <v>304</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>21</v>
@@ -3900,7 +4070,9 @@
         <v>24</v>
       </c>
       <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
+      <c r="K57" s="1" t="s">
+        <v>302</v>
+      </c>
       <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
         <v>274</v>
@@ -3918,15 +4090,15 @@
         <v>276</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>277</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C58" t="s">
+        <v>304</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>21</v>
@@ -3947,7 +4119,9 @@
         <v>24</v>
       </c>
       <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
+      <c r="K58" s="1" t="s">
+        <v>302</v>
+      </c>
       <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
         <v>244</v>
@@ -3965,15 +4139,15 @@
         <v>280</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>281</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>20</v>
+        <v>290</v>
+      </c>
+      <c r="C59" t="s">
+        <v>304</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>21</v>
@@ -3994,7 +4168,9 @@
         <v>24</v>
       </c>
       <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
+      <c r="K59" s="1" t="s">
+        <v>303</v>
+      </c>
       <c r="L59" s="1"/>
       <c r="M59" s="1" t="s">
         <v>283</v>
@@ -4014,7 +4190,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -4035,7 +4211,7 @@
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -4056,7 +4232,7 @@
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -4077,7 +4253,7 @@
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -4098,7 +4274,7 @@
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -4119,7 +4295,7 @@
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -4140,7 +4316,7 @@
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -4161,7 +4337,7 @@
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -4182,7 +4358,7 @@
       <c r="R67" s="1"/>
       <c r="S67" s="1"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -4203,7 +4379,7 @@
       <c r="R68" s="1"/>
       <c r="S68" s="1"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -4224,7 +4400,7 @@
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -4245,7 +4421,7 @@
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -4266,7 +4442,7 @@
       <c r="R71" s="1"/>
       <c r="S71" s="1"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -4287,7 +4463,7 @@
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -4308,7 +4484,7 @@
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -4329,7 +4505,7 @@
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -4350,7 +4526,7 @@
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -4371,7 +4547,7 @@
       <c r="R76" s="1"/>
       <c r="S76" s="1"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -4392,7 +4568,7 @@
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -4413,7 +4589,7 @@
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -4434,7 +4610,7 @@
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -4455,7 +4631,7 @@
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -4476,7 +4652,7 @@
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -4497,7 +4673,7 @@
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -4518,7 +4694,7 @@
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -4539,7 +4715,7 @@
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -4560,7 +4736,7 @@
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -4581,7 +4757,7 @@
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -4602,7 +4778,7 @@
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -4623,7 +4799,7 @@
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -4644,7 +4820,7 @@
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -4665,7 +4841,7 @@
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -4686,7 +4862,7 @@
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -4707,7 +4883,7 @@
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -4728,7 +4904,7 @@
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4749,7 +4925,7 @@
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -4770,7 +4946,7 @@
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4791,7 +4967,7 @@
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -4812,7 +4988,7 @@
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -4833,7 +5009,7 @@
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -4854,7 +5030,7 @@
       <c r="R99" s="1"/>
       <c r="S99" s="1"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -4875,7 +5051,7 @@
       <c r="R100" s="1"/>
       <c r="S100" s="1"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -4896,7 +5072,7 @@
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4917,7 +5093,7 @@
       <c r="R102" s="1"/>
       <c r="S102" s="1"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4938,7 +5114,7 @@
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -4959,7 +5135,7 @@
       <c r="R104" s="1"/>
       <c r="S104" s="1"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -4980,7 +5156,7 @@
       <c r="R105" s="1"/>
       <c r="S105" s="1"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -5001,7 +5177,7 @@
       <c r="R106" s="1"/>
       <c r="S106" s="1"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -5022,7 +5198,7 @@
       <c r="R107" s="1"/>
       <c r="S107" s="1"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -5043,7 +5219,7 @@
       <c r="R108" s="1"/>
       <c r="S108" s="1"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -5064,7 +5240,7 @@
       <c r="R109" s="1"/>
       <c r="S109" s="1"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -5085,7 +5261,7 @@
       <c r="R110" s="1"/>
       <c r="S110" s="1"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -5106,7 +5282,7 @@
       <c r="R111" s="1"/>
       <c r="S111" s="1"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -5127,7 +5303,7 @@
       <c r="R112" s="1"/>
       <c r="S112" s="1"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -5148,7 +5324,7 @@
       <c r="R113" s="1"/>
       <c r="S113" s="1"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -5169,7 +5345,7 @@
       <c r="R114" s="1"/>
       <c r="S114" s="1"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -5190,7 +5366,7 @@
       <c r="R115" s="1"/>
       <c r="S115" s="1"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -5211,7 +5387,7 @@
       <c r="R116" s="1"/>
       <c r="S116" s="1"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -5232,7 +5408,7 @@
       <c r="R117" s="1"/>
       <c r="S117" s="1"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -5253,7 +5429,7 @@
       <c r="R118" s="1"/>
       <c r="S118" s="1"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -5274,7 +5450,7 @@
       <c r="R119" s="1"/>
       <c r="S119" s="1"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -5295,7 +5471,7 @@
       <c r="R120" s="1"/>
       <c r="S120" s="1"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -5316,7 +5492,7 @@
       <c r="R121" s="1"/>
       <c r="S121" s="1"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -5337,7 +5513,7 @@
       <c r="R122" s="1"/>
       <c r="S122" s="1"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -5358,7 +5534,7 @@
       <c r="R123" s="1"/>
       <c r="S123" s="1"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -5379,7 +5555,7 @@
       <c r="R124" s="1"/>
       <c r="S124" s="1"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -5400,7 +5576,7 @@
       <c r="R125" s="1"/>
       <c r="S125" s="1"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -5421,7 +5597,7 @@
       <c r="R126" s="1"/>
       <c r="S126" s="1"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -5442,7 +5618,7 @@
       <c r="R127" s="1"/>
       <c r="S127" s="1"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -5463,7 +5639,7 @@
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -5484,7 +5660,7 @@
       <c r="R129" s="1"/>
       <c r="S129" s="1"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -5505,7 +5681,7 @@
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -5526,7 +5702,7 @@
       <c r="R131" s="1"/>
       <c r="S131" s="1"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -5547,7 +5723,7 @@
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -5568,7 +5744,7 @@
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -5589,7 +5765,7 @@
       <c r="R134" s="1"/>
       <c r="S134" s="1"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -5610,7 +5786,7 @@
       <c r="R135" s="1"/>
       <c r="S135" s="1"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -5631,7 +5807,7 @@
       <c r="R136" s="1"/>
       <c r="S136" s="1"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5652,7 +5828,7 @@
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5673,7 +5849,7 @@
       <c r="R138" s="1"/>
       <c r="S138" s="1"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -5694,7 +5870,7 @@
       <c r="R139" s="1"/>
       <c r="S139" s="1"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -5715,7 +5891,7 @@
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -5736,7 +5912,7 @@
       <c r="R141" s="1"/>
       <c r="S141" s="1"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -5757,7 +5933,7 @@
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5778,7 +5954,7 @@
       <c r="R143" s="1"/>
       <c r="S143" s="1"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5799,7 +5975,7 @@
       <c r="R144" s="1"/>
       <c r="S144" s="1"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5820,7 +5996,7 @@
       <c r="R145" s="1"/>
       <c r="S145" s="1"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5841,7 +6017,7 @@
       <c r="R146" s="1"/>
       <c r="S146" s="1"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5862,7 +6038,7 @@
       <c r="R147" s="1"/>
       <c r="S147" s="1"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5883,7 +6059,7 @@
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5904,7 +6080,7 @@
       <c r="R149" s="1"/>
       <c r="S149" s="1"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5925,7 +6101,7 @@
       <c r="R150" s="1"/>
       <c r="S150" s="1"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5946,7 +6122,7 @@
       <c r="R151" s="1"/>
       <c r="S151" s="1"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5967,7 +6143,7 @@
       <c r="R152" s="1"/>
       <c r="S152" s="1"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5988,7 +6164,7 @@
       <c r="R153" s="1"/>
       <c r="S153" s="1"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -6009,7 +6185,7 @@
       <c r="R154" s="1"/>
       <c r="S154" s="1"/>
     </row>
-    <row r="155">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -6030,7 +6206,7 @@
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
     </row>
-    <row r="156">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -6051,7 +6227,7 @@
       <c r="R156" s="1"/>
       <c r="S156" s="1"/>
     </row>
-    <row r="157">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -6072,7 +6248,7 @@
       <c r="R157" s="1"/>
       <c r="S157" s="1"/>
     </row>
-    <row r="158">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -6093,7 +6269,7 @@
       <c r="R158" s="1"/>
       <c r="S158" s="1"/>
     </row>
-    <row r="159">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -6114,7 +6290,7 @@
       <c r="R159" s="1"/>
       <c r="S159" s="1"/>
     </row>
-    <row r="160">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -6135,7 +6311,7 @@
       <c r="R160" s="1"/>
       <c r="S160" s="1"/>
     </row>
-    <row r="161">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -6156,7 +6332,7 @@
       <c r="R161" s="1"/>
       <c r="S161" s="1"/>
     </row>
-    <row r="162">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -6177,7 +6353,7 @@
       <c r="R162" s="1"/>
       <c r="S162" s="1"/>
     </row>
-    <row r="163">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -6198,7 +6374,7 @@
       <c r="R163" s="1"/>
       <c r="S163" s="1"/>
     </row>
-    <row r="164">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -6219,7 +6395,7 @@
       <c r="R164" s="1"/>
       <c r="S164" s="1"/>
     </row>
-    <row r="165">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -6240,7 +6416,7 @@
       <c r="R165" s="1"/>
       <c r="S165" s="1"/>
     </row>
-    <row r="166">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -6261,7 +6437,7 @@
       <c r="R166" s="1"/>
       <c r="S166" s="1"/>
     </row>
-    <row r="167">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -6282,7 +6458,7 @@
       <c r="R167" s="1"/>
       <c r="S167" s="1"/>
     </row>
-    <row r="168">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -6303,7 +6479,7 @@
       <c r="R168" s="1"/>
       <c r="S168" s="1"/>
     </row>
-    <row r="169">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -6324,7 +6500,7 @@
       <c r="R169" s="1"/>
       <c r="S169" s="1"/>
     </row>
-    <row r="170">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -6345,7 +6521,7 @@
       <c r="R170" s="1"/>
       <c r="S170" s="1"/>
     </row>
-    <row r="171">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6366,7 +6542,7 @@
       <c r="R171" s="1"/>
       <c r="S171" s="1"/>
     </row>
-    <row r="172">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6387,7 +6563,7 @@
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
     </row>
-    <row r="173">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6408,7 +6584,7 @@
       <c r="R173" s="1"/>
       <c r="S173" s="1"/>
     </row>
-    <row r="174">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6429,7 +6605,7 @@
       <c r="R174" s="1"/>
       <c r="S174" s="1"/>
     </row>
-    <row r="175">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -6450,7 +6626,7 @@
       <c r="R175" s="1"/>
       <c r="S175" s="1"/>
     </row>
-    <row r="176">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -6471,7 +6647,7 @@
       <c r="R176" s="1"/>
       <c r="S176" s="1"/>
     </row>
-    <row r="177">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -6492,7 +6668,7 @@
       <c r="R177" s="1"/>
       <c r="S177" s="1"/>
     </row>
-    <row r="178">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -6513,7 +6689,7 @@
       <c r="R178" s="1"/>
       <c r="S178" s="1"/>
     </row>
-    <row r="179">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6534,7 +6710,7 @@
       <c r="R179" s="1"/>
       <c r="S179" s="1"/>
     </row>
-    <row r="180">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6555,7 +6731,7 @@
       <c r="R180" s="1"/>
       <c r="S180" s="1"/>
     </row>
-    <row r="181">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6576,7 +6752,7 @@
       <c r="R181" s="1"/>
       <c r="S181" s="1"/>
     </row>
-    <row r="182">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6597,7 +6773,7 @@
       <c r="R182" s="1"/>
       <c r="S182" s="1"/>
     </row>
-    <row r="183">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6618,7 +6794,7 @@
       <c r="R183" s="1"/>
       <c r="S183" s="1"/>
     </row>
-    <row r="184">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6639,7 +6815,7 @@
       <c r="R184" s="1"/>
       <c r="S184" s="1"/>
     </row>
-    <row r="185">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6660,7 +6836,7 @@
       <c r="R185" s="1"/>
       <c r="S185" s="1"/>
     </row>
-    <row r="186">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6681,7 +6857,7 @@
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
     </row>
-    <row r="187">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -6702,7 +6878,7 @@
       <c r="R187" s="1"/>
       <c r="S187" s="1"/>
     </row>
-    <row r="188">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -6723,7 +6899,7 @@
       <c r="R188" s="1"/>
       <c r="S188" s="1"/>
     </row>
-    <row r="189">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -6744,7 +6920,7 @@
       <c r="R189" s="1"/>
       <c r="S189" s="1"/>
     </row>
-    <row r="190">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -6765,7 +6941,7 @@
       <c r="R190" s="1"/>
       <c r="S190" s="1"/>
     </row>
-    <row r="191">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -6786,7 +6962,7 @@
       <c r="R191" s="1"/>
       <c r="S191" s="1"/>
     </row>
-    <row r="192">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -6807,7 +6983,7 @@
       <c r="R192" s="1"/>
       <c r="S192" s="1"/>
     </row>
-    <row r="193">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -6828,7 +7004,7 @@
       <c r="R193" s="1"/>
       <c r="S193" s="1"/>
     </row>
-    <row r="194">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -6849,7 +7025,7 @@
       <c r="R194" s="1"/>
       <c r="S194" s="1"/>
     </row>
-    <row r="195">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -6870,7 +7046,7 @@
       <c r="R195" s="1"/>
       <c r="S195" s="1"/>
     </row>
-    <row r="196">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -6891,7 +7067,7 @@
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
     </row>
-    <row r="197">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -6912,7 +7088,7 @@
       <c r="R197" s="1"/>
       <c r="S197" s="1"/>
     </row>
-    <row r="198">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -6933,7 +7109,7 @@
       <c r="R198" s="1"/>
       <c r="S198" s="1"/>
     </row>
-    <row r="199">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -6954,7 +7130,7 @@
       <c r="R199" s="1"/>
       <c r="S199" s="1"/>
     </row>
-    <row r="200">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -6975,7 +7151,7 @@
       <c r="R200" s="1"/>
       <c r="S200" s="1"/>
     </row>
-    <row r="201">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -6996,7 +7172,7 @@
       <c r="R201" s="1"/>
       <c r="S201" s="1"/>
     </row>
-    <row r="202">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -7017,7 +7193,7 @@
       <c r="R202" s="1"/>
       <c r="S202" s="1"/>
     </row>
-    <row r="203">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -7038,7 +7214,7 @@
       <c r="R203" s="1"/>
       <c r="S203" s="1"/>
     </row>
-    <row r="204">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7059,7 +7235,7 @@
       <c r="R204" s="1"/>
       <c r="S204" s="1"/>
     </row>
-    <row r="205">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7080,7 +7256,7 @@
       <c r="R205" s="1"/>
       <c r="S205" s="1"/>
     </row>
-    <row r="206">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7101,7 +7277,7 @@
       <c r="R206" s="1"/>
       <c r="S206" s="1"/>
     </row>
-    <row r="207">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7122,7 +7298,7 @@
       <c r="R207" s="1"/>
       <c r="S207" s="1"/>
     </row>
-    <row r="208">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7143,7 +7319,7 @@
       <c r="R208" s="1"/>
       <c r="S208" s="1"/>
     </row>
-    <row r="209">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7164,7 +7340,7 @@
       <c r="R209" s="1"/>
       <c r="S209" s="1"/>
     </row>
-    <row r="210">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -7185,7 +7361,7 @@
       <c r="R210" s="1"/>
       <c r="S210" s="1"/>
     </row>
-    <row r="211">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -7206,7 +7382,7 @@
       <c r="R211" s="1"/>
       <c r="S211" s="1"/>
     </row>
-    <row r="212">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -7227,7 +7403,7 @@
       <c r="R212" s="1"/>
       <c r="S212" s="1"/>
     </row>
-    <row r="213">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -7248,7 +7424,7 @@
       <c r="R213" s="1"/>
       <c r="S213" s="1"/>
     </row>
-    <row r="214">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7269,7 +7445,7 @@
       <c r="R214" s="1"/>
       <c r="S214" s="1"/>
     </row>
-    <row r="215">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7290,7 +7466,7 @@
       <c r="R215" s="1"/>
       <c r="S215" s="1"/>
     </row>
-    <row r="216">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7311,7 +7487,7 @@
       <c r="R216" s="1"/>
       <c r="S216" s="1"/>
     </row>
-    <row r="217">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7332,7 +7508,7 @@
       <c r="R217" s="1"/>
       <c r="S217" s="1"/>
     </row>
-    <row r="218">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7353,7 +7529,7 @@
       <c r="R218" s="1"/>
       <c r="S218" s="1"/>
     </row>
-    <row r="219">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -7374,7 +7550,7 @@
       <c r="R219" s="1"/>
       <c r="S219" s="1"/>
     </row>
-    <row r="220">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -7395,7 +7571,7 @@
       <c r="R220" s="1"/>
       <c r="S220" s="1"/>
     </row>
-    <row r="221">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -7416,7 +7592,7 @@
       <c r="R221" s="1"/>
       <c r="S221" s="1"/>
     </row>
-    <row r="222">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -7437,7 +7613,7 @@
       <c r="R222" s="1"/>
       <c r="S222" s="1"/>
     </row>
-    <row r="223">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -7458,7 +7634,7 @@
       <c r="R223" s="1"/>
       <c r="S223" s="1"/>
     </row>
-    <row r="224">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -7479,7 +7655,7 @@
       <c r="R224" s="1"/>
       <c r="S224" s="1"/>
     </row>
-    <row r="225">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -7500,7 +7676,7 @@
       <c r="R225" s="1"/>
       <c r="S225" s="1"/>
     </row>
-    <row r="226">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -7521,7 +7697,7 @@
       <c r="R226" s="1"/>
       <c r="S226" s="1"/>
     </row>
-    <row r="227">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -7542,7 +7718,7 @@
       <c r="R227" s="1"/>
       <c r="S227" s="1"/>
     </row>
-    <row r="228">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -7563,7 +7739,7 @@
       <c r="R228" s="1"/>
       <c r="S228" s="1"/>
     </row>
-    <row r="229">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -7584,7 +7760,7 @@
       <c r="R229" s="1"/>
       <c r="S229" s="1"/>
     </row>
-    <row r="230">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -7605,7 +7781,7 @@
       <c r="R230" s="1"/>
       <c r="S230" s="1"/>
     </row>
-    <row r="231">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -7626,7 +7802,7 @@
       <c r="R231" s="1"/>
       <c r="S231" s="1"/>
     </row>
-    <row r="232">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -7647,7 +7823,7 @@
       <c r="R232" s="1"/>
       <c r="S232" s="1"/>
     </row>
-    <row r="233">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -7668,7 +7844,7 @@
       <c r="R233" s="1"/>
       <c r="S233" s="1"/>
     </row>
-    <row r="234">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -7689,7 +7865,7 @@
       <c r="R234" s="1"/>
       <c r="S234" s="1"/>
     </row>
-    <row r="235">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -7710,7 +7886,7 @@
       <c r="R235" s="1"/>
       <c r="S235" s="1"/>
     </row>
-    <row r="236">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -7731,7 +7907,7 @@
       <c r="R236" s="1"/>
       <c r="S236" s="1"/>
     </row>
-    <row r="237">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -7752,7 +7928,7 @@
       <c r="R237" s="1"/>
       <c r="S237" s="1"/>
     </row>
-    <row r="238">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -7773,7 +7949,7 @@
       <c r="R238" s="1"/>
       <c r="S238" s="1"/>
     </row>
-    <row r="239">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -7794,7 +7970,7 @@
       <c r="R239" s="1"/>
       <c r="S239" s="1"/>
     </row>
-    <row r="240">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -7815,7 +7991,7 @@
       <c r="R240" s="1"/>
       <c r="S240" s="1"/>
     </row>
-    <row r="241">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -7836,7 +8012,7 @@
       <c r="R241" s="1"/>
       <c r="S241" s="1"/>
     </row>
-    <row r="242">
+    <row r="242" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -7857,7 +8033,7 @@
       <c r="R242" s="1"/>
       <c r="S242" s="1"/>
     </row>
-    <row r="243">
+    <row r="243" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -7878,7 +8054,7 @@
       <c r="R243" s="1"/>
       <c r="S243" s="1"/>
     </row>
-    <row r="244">
+    <row r="244" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -7899,7 +8075,7 @@
       <c r="R244" s="1"/>
       <c r="S244" s="1"/>
     </row>
-    <row r="245">
+    <row r="245" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -7920,7 +8096,7 @@
       <c r="R245" s="1"/>
       <c r="S245" s="1"/>
     </row>
-    <row r="246">
+    <row r="246" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -7941,7 +8117,7 @@
       <c r="R246" s="1"/>
       <c r="S246" s="1"/>
     </row>
-    <row r="247">
+    <row r="247" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -7962,7 +8138,7 @@
       <c r="R247" s="1"/>
       <c r="S247" s="1"/>
     </row>
-    <row r="248">
+    <row r="248" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -7983,7 +8159,7 @@
       <c r="R248" s="1"/>
       <c r="S248" s="1"/>
     </row>
-    <row r="249">
+    <row r="249" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -8004,7 +8180,7 @@
       <c r="R249" s="1"/>
       <c r="S249" s="1"/>
     </row>
-    <row r="250">
+    <row r="250" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -8025,7 +8201,7 @@
       <c r="R250" s="1"/>
       <c r="S250" s="1"/>
     </row>
-    <row r="251">
+    <row r="251" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -8046,7 +8222,7 @@
       <c r="R251" s="1"/>
       <c r="S251" s="1"/>
     </row>
-    <row r="252">
+    <row r="252" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -8067,7 +8243,7 @@
       <c r="R252" s="1"/>
       <c r="S252" s="1"/>
     </row>
-    <row r="253">
+    <row r="253" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -8088,7 +8264,7 @@
       <c r="R253" s="1"/>
       <c r="S253" s="1"/>
     </row>
-    <row r="254">
+    <row r="254" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -8109,7 +8285,7 @@
       <c r="R254" s="1"/>
       <c r="S254" s="1"/>
     </row>
-    <row r="255">
+    <row r="255" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -8130,7 +8306,7 @@
       <c r="R255" s="1"/>
       <c r="S255" s="1"/>
     </row>
-    <row r="256">
+    <row r="256" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -8151,7 +8327,7 @@
       <c r="R256" s="1"/>
       <c r="S256" s="1"/>
     </row>
-    <row r="257">
+    <row r="257" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -8172,7 +8348,7 @@
       <c r="R257" s="1"/>
       <c r="S257" s="1"/>
     </row>
-    <row r="258">
+    <row r="258" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -8193,7 +8369,7 @@
       <c r="R258" s="1"/>
       <c r="S258" s="1"/>
     </row>
-    <row r="259">
+    <row r="259" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -8215,8 +8391,8 @@
       <c r="S259" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S59"/>
+  <autoFilter ref="A1:S59" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>